--- a/ae_ai_summaries.xlsx
+++ b/ae_ai_summaries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Summaries" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AI Summaries" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,11 +499,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="109" customHeight="1">
+          <t>2026-06-09 04:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="104" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>S40835</t>
@@ -516,17 +516,16 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Inverter 1 has not reported since Apr 6 at 10:57 AM EDT, a confirmed outage (~63 days). The meter-to-inverter ratio is 0.97, consistent with one of 20 inverters fully offline rather than a comm-only loss.
-The remaining 19 inverters are producing in line with peers through the afternoon of Jun 8, and the meter is tracking expected output.
-Estimated loss for Inv 1: ~14 MWh over ~63 days (~5% site capacity, ~225 kWh/day expected per PV model losses for the sampled unit).
-30-day EPI averages 0.92 and availability is 95%, both reflecting the Inv 1 outage.
-Monitoring flags: a meter current-mismatch alert on the Main production meter triggered Jun 8 at 6:19 PM (A/B/C = 85/105/99 A); worth a CT/wiring check. Rule tool also notes Inv 12 residual loss and minor soiling.
-Weather: light rain through Jun 11, highs 81â93Â°F â modest production impact expected.[DONE]</t>
+          <t>Inverter 1 has been offline since Apr 6 at 10:57 AM EDT â the meter-to-inverter ratio of 0.97 confirms a sustained outage rather than a comm-only issue. The remaining 19 inverters are online and producing normally as of this evening, with the site currently under light rain at 72Â°F.
+The Inverter 1 outage is the only ongoing event: ~5% of site capacity unavailable for ~63 days, roughly 14 MWh lost to date (~228 kWh/day expected on the sampled inverter).
+30-day EPI averages 0.92 and inverter availability is 95%, both consistent with one inverter down.
+Meter-to-inverter ratio is 0.97 (normal). Rule tool flags 5% soiling loss on the main meter and 29% residual loss on Inverter 12 â worth monitoring.
+Forecast: light rain through Jun 9, rain Jun 10, warming to 95Â°F by Jun 11 â reduced output likely early week.[DONE]</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:54 UTC</t>
+          <t>2026-06-09 04:14 UTC</t>
         </is>
       </c>
     </row>
@@ -551,7 +550,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:54 UTC</t>
+          <t>2026-06-09 04:14 UTC</t>
         </is>
       </c>
     </row>
@@ -576,7 +575,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:54 UTC</t>
+          <t>2026-06-09 04:14 UTC</t>
         </is>
       </c>
     </row>
@@ -602,7 +601,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:54 UTC</t>
+          <t>2026-06-09 04:14 UTC</t>
         </is>
       </c>
     </row>
@@ -629,7 +628,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:54 UTC</t>
+          <t>2026-06-09 04:14 UTC</t>
         </is>
       </c>
     </row>
@@ -655,7 +654,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:55 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -681,7 +680,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:55 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -706,7 +705,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:55 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -732,7 +731,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:55 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -758,7 +757,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:55 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -784,7 +783,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:56 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -809,7 +808,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:56 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -835,7 +834,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:56 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -860,7 +859,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:56 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -885,7 +884,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:56 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -911,7 +910,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:57 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -936,7 +935,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:57 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -961,7 +960,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:57 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -987,11 +986,11 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:58 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="86" customHeight="1">
+          <t>2026-06-09 04:15 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="94" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>S65216</t>
@@ -1004,16 +1003,16 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 8 at 4:11 PM PDT, and Inverter 1 is producing in line with expectations under light rain conditions.
-Today's output tracks expected through 3 PM, with peak hourly production around 1.7 MW under cloudy skies. No production events identified in the reporting period.
-30-day Energy Performance Index averages 0.99 and inverter availability is 99%, with production at 99% of estimate. No major losses identified in the PV model or tracker loss data.
-Meter-to-inverter ratio is 0.99, normal. No active alerts or rule tool warnings.
-Light rain continues Jun 9, with clear skies and warming to 79Â°F expected Jun 10â11, favorable for production.[DONE]</t>
+          <t>All hardware is communicating as of Jun 8 at 8:28 PM PDT, including Inverter 1, the production meter, and weather sensors. The site is producing through light rain today, with cloud-driven variability visible in hourly production versus expected. No production events identified.
+Over the last 30 days, the Energy Performance Index averaged 1.00 and inverter availability was 99%, with a brief dip to 85% on May 28.
+Site production totaled 99% of estimate. No major losses identified in the sampled-inverter model; tracker losses were minimal (~3â28 kWh/day).
+Meter-to-inverter ratio is 0.99, which is normal. No active alerts.
+Forecast shows light rain Jun 9, then clear skies Jun 10â11 with highs reaching 77Â°F, favorable for production.[DONE]</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:58 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1038,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:58 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1063,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:58 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1089,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:58 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1115,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:59 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1141,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:59 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1167,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:59 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1193,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:59 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1219,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:59 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1245,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 02:59 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1270,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:00 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1295,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 03:00 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1321,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:00 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1347,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 03:00 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1373,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:00 UTC</t>
+          <t>2026-06-09 04:15 UTC</t>
         </is>
       </c>
     </row>

--- a/ae_ai_summaries.xlsx
+++ b/ae_ai_summaries.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="103" customHeight="1">
+    <row r="2" ht="101" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>S40834</t>
@@ -489,21 +489,20 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>All 11 Solectria PVI 28TL inverters are online and producing normally as of Jun 8 at 9:08 PM EDT, with site time after sunset.
-Today's production tracked expected output well under variable cloud cover from light rain, peaking around 240 kW midday.
-30-day Energy Performance Index averaged 0.87 with inverter availability at 100%.
-Sampled-inverter PV model losses show ~5% DC/AC age and 7% residual; no major losses identified.
-Meter-to-inverter ratio is 0.97, normal. The Weather Station (Standard) ambient temperature is stuck at -20.2Â°F, a sensor data quality issue that may affect expected energy modeling. A stale Jul 2025 rule tool alert remains open with no production correlation.
-Forecast calls for rain and highs climbing to 95Â°F by Jun 11; expect variable output and possible thermal derating late week.[DONE]</t>
+          <t>All 11 Solectria PVI 28TL inverters online and producing normally as of Jun 9 at 11:22 AM EDT, with the meter, weather station, and gateway all reporting within the last few minutes.
+Current conditions are light rain at 75Â°F, consistent with today's lower production trend and reduced irradiance.
+The 30-day Energy Performance Index averages 0.87 with inverter availability at 100%. Sampled-inverter PV model losses are dominated by DC/AC age (~5% each) and a 7% residual, consistent with the EPI gap.
+Meter-to-inverter ratio is 0.97, normal. The Weather Station (Standard) ambient temperature is stuck at -20.2Â°F per the rule tool; this affects expected-energy modeling and should be reviewed.
+Forecast is light rain with highs 88â91Â°F through Jun 12 â expect continued variable, reduced output.[DONE]</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:14 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="104" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="95" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>S40835</t>
@@ -516,20 +515,21 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Inverter 1 has been offline since Apr 6 at 10:57 AM EDT â the meter-to-inverter ratio of 0.97 confirms a sustained outage rather than a comm-only issue. The remaining 19 inverters are online and producing normally as of this evening, with the site currently under light rain at 72Â°F.
-The Inverter 1 outage is the only ongoing event: ~5% of site capacity unavailable for ~63 days, roughly 14 MWh lost to date (~228 kWh/day expected on the sampled inverter).
-30-day EPI averages 0.92 and inverter availability is 95%, both consistent with one inverter down.
-Meter-to-inverter ratio is 0.97 (normal). Rule tool flags 5% soiling loss on the main meter and 29% residual loss on Inverter 12 â worth monitoring.
-Forecast: light rain through Jun 9, rain Jun 10, warming to 95Â°F by Jun 11 â reduced output likely early week.[DONE]</t>
+          <t>Inverter 1 has been offline since Apr 6 at 11:01 AM EDT (last upload Apr 6 at 10:57 AM). The meter-to-inverter ratio of 0.97 over 30 days confirms a true outage, not a communication loss.
+The other 19 inverters are online and producing in line with expected output under light rain conditions (75Â°F).
+Inverter 1 outage: ~36 kW offline (~5% of site), ~64 days, ~13 MWh lost (~200 kWh/day expected per PV model for the sampled inverter).
+30-day EPI averages 0.92 and availability holds at 95%, both reflecting the Inverter 1 outage.
+Meter-to-inverter ratio is 0.97 (normal). Rule tool also flags Inverter 12 with 29% excessive residual loss â worth monitoring.
+Light rain forecast through Jun 12 with highs 88â91Â°F; modest production impact expected.[DONE]</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:14 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="107" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="97" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>S40836</t>
@@ -542,19 +542,20 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>All 13 Solectria inverters are online and producing, with last uploads between 8:52 PM and 9:12 PM EDT on Jun 8. Meter, weather stations, and gateway are all current as of 10:52 PM. Light rain is present at the site, and the sun is down.
-30-day Energy Performance Index averages 0.88 with inverter availability at 100%. Sampled-inverter PV model losses are dominated by DC/AC age (~5% each) and residual (~10%), consistent with a mature system.
-Meter-to-inverter ratio is 0.97, normal. An Info-level meter phase alert triggered at 9:05 PM on near-zero power â a nighttime artifact. Weather Station 2 module temperature is stuck at -40Â°F per the rule tool; worth investigating but not affecting expected energy.
-Forecast: light rain to rain through Jun 11 with highs rising to 93Â°F. Expect variable production and possible mild thermal derate Jun 11.[DONE]</t>
+          <t>All 13 Solectria 28kW inverters online and producing as of Jun 9 at 11:22 AM EDT under light rain, with site output tracking expected energy closely this morning.
+No production events in the last two weeks. Daily output has varied with weather, including low-irradiance days on May 20â22 and May 24.
+30-day Energy Performance Index averages 0.88 with inverter availability at 100%. Sampled-inverter PV model losses show DC/AC age (~5% each) and ~10% residual; no snow or downtime losses.
+Meter-to-inverter ratio is 0.97 (normal). Rule tool flags Weather Station 2 module temperature stuck at -40Â°F â sensor needs review as it may affect expected energy modeling.
+Forecast calls for light rain and highs of 86â90Â°F through Jun 12; expect reduced but normal output.[DONE]</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:14 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="113" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>S44485</t>
@@ -567,19 +568,19 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>All 66 inverters are online and the site is operating normally as of Jun 8 at 10:54 PM EDT, with end-of-day telemetry consistent across both sites. Today's production reached 33,766 kWh, with peak hourly output near 4 MW around midday â typical for clear conditions.
-Over the last 30 days, the site has performed well: EPI averaged 1.04, inverter availability averaged 100%, and meter production totaled 840 MWh, 108% of estimate. No major losses identified on the sampled inverter.
-Meter-to-inverter ratio is 1.00, normal. The only open item is an Info-level report run-time warning from Mar 24 on the Site 1 production meter â stale, no production correlation. Rule tool flags the KYZ Pulse Meter at 0% availability; meter telemetry is current, so this appears to be a configuration flag rather than an outage.
-Forecast calls for rain and light rain Jun 9â11, with reduced production expected.[DONE]</t>
+          <t>All 66 inverters online and producing normally as of Jun 9 at 11:24 AM EDT, with light rain and overcast conditions reducing today's output as expected.
+Site is healthy. The 30-day Energy Performance Index averages 1.05, and inverter availability is 100% over the last 7 days (30-day average 99.8%). Production totaled 838 MWh, 107% of estimate. No major losses identified on the sampled inverter.
+Meter-to-inverter ratio is 1.00, normal. The rule tool flags high energy ratios (1.10â1.14) on many inverters and both production meters, suggesting possible PV model or weather station calibration drift worth reviewing. The KYZ Pulse Meter shows 0% availability per the rule tool; verify whether this device is in service.
+Forecast calls for light rain and showers through Jun 12 with highs 73â81Â°F, so reduced output is expected to continue near-term before clearing.[DONE]</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:14 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="88" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="104" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>S44566</t>
@@ -592,20 +593,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>All 27 Chint inverters are online with last updates around Jun 8 at 9:06 PM EDT, and the site produced 12,820 kWh today against an estimate of ~11,083 kWh. Current conditions are clear and 64Â°F after sunset.
-30-day EPI averages ~1.10 and inverter availability is 94%, pulled down by a site-wide outage May 27â29 (~25 MWh lost: 3 days, ~11 MWh/day expected, full site affected).
-The sustained EPI above 1.1 and the rule tool's high energy ratio flags on six inverters suggest a PV model or POA sensor calibration issue worth review.
-Meter-to-inverter ratio is 0.99, normal.
-Forecast shows rain and light rain Jun 9â11 with highs 75â79Â°F, which will reduce production but pose no equipment risk.[DONE]</t>
+          <t>All 27 Chint SCA60KTL inverters are online and reporting as of Jun 9 at 11:24 AM EDT, with the site producing normally under light rain. Today's production is tracking expected output through the morning given overcast conditions.
+30-day Energy Performance Index averages near 1.10 on normal-insolation days, and inverter availability is 94%, pulled down by reduced availability May 27â29. Sampled-inverter losses show no notable issues outside that window.
+Meter-to-inverter ratio is 0.99, normal. The rule tool flags high energy ratios on 6 inverters and low diffuse shade factors site-wide â consistent with the elevated EPI, suggesting a PV model or POA sensor calibration review is warranted.
+Forecast calls for light rain and rain through Jun 12 with mild temperatures (61â82Â°F); expect reduced but normal production.[DONE]</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:14 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="92" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>S44882</t>
@@ -618,21 +618,20 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Inverter 20 has been offline since May 30, confirmed by zero production and an Insulation Resistance Low fault (IsolationErr) that re-triggered Jun 7 at 6:30 AM EDT.
-This is a forced outage affecting ~73 kW (~4% of site). Estimated loss since May 30 is ~3.8 MWh (10 days, ~380 kWh/day per PV model losses for the sampled inverter).
-The other 26 inverters are producing normally; site hit ~1.6 MW peak today under clear skies.
-30-day EPI averages 1.18 and availability 96%. Persistently high EPI and rule tool "energy above expected" (+22%) suggest a PV model or irradiance sensor calibration issue worth review.
-Meter-to-inverter ratio is 0.99 (normal).
-Forecast: clear Jun 9 (79Â°F), light rain Jun 10â11 will reduce output.[DONE]</t>
+          <t>Inverter 20 has been offline since May 31, classified as a forced outage (Insulation Resistance Low / IsolationErr fault). The remaining 26 inverters are producing normally as of Jun 9 at 11:25 AM EDT under clear skies, 73Â°F.
+Impact to date: ~3.5 MWh lost (~10 days, ~1/27 of capacity, ~390 kWh/day per PV model losses for the sampled inverter 20). Site availability has held at 96% since the trip.
+30-day production totaled 286 MWh (113% of estimate). EPI averaged 1.18, persistently above 1.1 across all days â this suggests a PV model or weather station calibration issue worth review.
+Meter-to-inverter ratio is 0.99, normal. Rule tool flags high energy ratio and excessive negative residual losses across most inverters, consistent with the EPI calibration finding.
+Forecast: light rain Jun 10â12 with highs reaching 90Â°F by Jun 12; expect reduced output and possible heat derating.[DONE]</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:14 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="113" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="112" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>S51957</t>
@@ -645,20 +644,20 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>All three CPS SCA60KTL inverters are online and producing as of Jun 8 at 9:25 PM EDT, with the meter, weather station, and logger reporting current. Today's peak hourly output reached ~155 kW around midday under variable cloud cover.
-The site shows a sustained underperformance pattern. Energy Performance Index has averaged ~0.42 over 30 days, and actual vs. expected production is tracking at 49% over the past 7 days.
-PV model losses on the sampled inverter show large DC/AC age losses (~80%+) plus ~58% residual loss, suggesting a model configuration or long-term degradation issue worth review.
-Inverter availability is 100% over 30 days and the meter-to-inverter ratio is 1.00, both normal. Active performance and rule tool alerts reflect the underperformance noted above.
-Forecast: light rain Jun 9â11 with highs 79â90Â°F; expect reduced output and possible mild thermal derating Jun 11.[DONE]</t>
+          <t>All three CPS SCA60KTL inverters are online and producing as of Jun 9 at 9:31 AM EDT, with the data logger reporting at 11:24 AM. Current conditions are clear and 75Â°F.
+However, the site is materially underperforming. The Energy Performance Index has averaged roughly 0.41 over 30 days, with actual production at 49% of expected over the last 7 days. All three inverters show energy ratios near 0.45â0.49 in the rule tool, indicating a site-wide shortfall rather than a single-inverter event.
+PV model losses on the sampled Inverter-1 attribute the gap to large DC/AC age losses (~85%) and ~58% residual losses, with no snow or downtime â suggesting a model calibration concern or sustained derate worth investigating.
+Inverter availability is 100% recently; meter-to-inverter ratio is 1.00 (normal).
+Light rain and highs near 90Â°F are forecast Jun 10â12, expect reduced output.[DONE]</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="101" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>S51958</t>
@@ -671,20 +670,20 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>All three inverters are online and producing normally as of Jun 8 at 10:04 PM EDT, with the site having logged 1,033 kWh today against an estimate of 1,021 kWh. Conditions are clear and 63Â°F after sunset.
-Production tracked expected output closely over the last two days with no inverter dropouts.
-Trailing 30-day Energy Performance Index averages 0.95 and inverter availability is 100%. Sampled-inverter losses show modest DC/AC age (~3% each) and soiling (~1%) â no major losses identified.
-Meter-to-inverter ratio is 1.00, normal. Rule tool flags missing default alert configuration on the Microhard Modem â a monitoring setup item, no production impact.
-Forecast calls for light rain Jun 9â11 with highs rising from 79Â°F to 90Â°F; expect reduced output on overcast hours but no equipment risk.[DONE]</t>
+          <t>All three inverters online and producing as of Jun 9 at 10:08 AM EDT under clear skies (75Â°F). Hardware is communicating normally.
+Site is healthy. The 30-day Energy Performance Index averages 0.94, with inverter availability at 100%.
+Actual vs. expected production tracked at 96% over the last 7 days, and all three inverters are producing in proportion to their ratings. Sampled-inverter PV model losses show only minor age and soiling effects.
+Meter-to-inverter ratio is 1.00, normal. Rule tool flags two configuration items on the Microhard Modem (default alerts not set) â monitoring setup only, no production impact.
+Light rain and highs near 90Â°F are forecast Jun 10â12, which will likely reduce production modestly.[DONE]</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="97" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="108" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>S51959</t>
@@ -697,19 +696,20 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Both inverters are online with last telemetry at 8:58 PM EDT on Jun 8, and today's production reached 751 kWh versus an estimate of 678 kWh. It is currently nighttime and clear at 63Â°F.
-30-day EPI averages 0.83 and inverter availability is 100%. Total production of 18,416 kWh tracks at 90% of estimate. The sampled inverter shows residual losses of -26%, indicating the PV model is under-predicting actual output.
-Meter-to-inverter ratio is 1.00, normal. The rule tool flags high energy ratios on both inverters (1.11 and 1.19) and a production meter capacity configuration mismatch â these point to a model or nameplate calibration issue rather than a field problem.
-Forecast calls for light rain Jun 9â11 with highs 79â90Â°F, which will reduce output modestly.[DONE]</t>
+          <t>All hardware is communicating as of Jun 9 at 11:14 AM EDT, with both inverters reporting through 11:04 AM. Current conditions are clear and 75Â°F, and midday production is tracking actual vs. expected output normally.
+No production events occurred in the reporting period.
+The 30-day Energy Performance Index averaged 0.83, with inverter availability at 100%. Site totals reached 89% of estimated energy. The sampled inverter PV model losses show a residual loss of â26%, indicating actual production is exceeding the model.
+The meter-to-inverter ratio is 1.00, normal. The rule tool flags a high energy ratio (1.21 and 1.30) on both inverters and a production meter capacity mismatch, suggesting PV model or capacity configuration needs review. No active alerts.
+Light rain is forecast Jun 10â12 with highs to 91Â°F, which may modestly reduce production.[DONE]</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="112" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="114" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>S51960</t>
@@ -722,20 +722,19 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>All 5 inverters online and producing normally as of Jun 8 at 10:30 PM EDT, with peak output near 248 kW around 1:00 PM under clear skies. Nighttime now; conditions favorable today produced 1,829 kWh, close to the 1,903 kWh estimate.
-No production events in the reporting period.
-30-day Energy Performance Index averages 0.78, with inverter availability at 100%. Actual-to-estimate ratio is 79%. The sampled inverter shows residual loss of 8% and soiling loss of 3% in PV model losses, suggesting modest persistent underperformance site-wide.
-Meter-to-inverter ratio is 0.99, normal. Rule tool flags Inverters 2 and 3 with low energy ratios (0.69 and 0.65) and elevated residual loss versus peers â worth monitoring for relative underperformance. A low-severity Performance Index alert is active (0.79).
-Light rain forecast Jun 9â11 with warming temperatures; reduced production expected.[DONE]</t>
+          <t>All five inverters are online and producing as of Jun 9 at 10:36 AM EDT under clear skies (75Â°F). Current hourly output through 10 AM is tracking reduced irradiance this morning, consistent with variable cloud cover earlier in the day.
+Over the last 30 days, the Energy Performance Index averaged about 0.77, with inverter availability at 100%. Sampled Inverter-1 PV model losses show residual loss of 7% plus soiling 3%, suggesting a site-wide cleaning may be worth evaluating.
+The rule tool flags Inverters 2 and 3 with low energy ratios (0.69 and 0.65) and elevated residual losses (29% and 33%) versus peers â consistent underperformance visible in the hourly production chart. Meter-to-inverter ratio is 0.99 (normal). A low-priority Performance Index alert from Jun 8 reflects this ongoing pattern.
+Forecast calls for rain Jun 10â12 with highs near 90Â°F; expect reduced production those days.[DONE]</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="101" customHeight="1">
+          <t>2026-06-09 17:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="99" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>S54553</t>
@@ -748,20 +747,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Inverter SMA SC4000 and all site hardware are communicating normally as of Jun 8 at 7:55 PM PDT, with the inverter producing 8,930 kWh today under light rain conditions. Production tracked expected output closely through the day.
-30-day Energy Performance Index averaged 1.00 and inverter availability was 100%.
-Site produced 1,082 MWh against a 933 MWh estimate (116%). PV model losses show only routine age and soiling losses; tracker losses were negligible.
-Meter-to-inverter ratio is 0.99 (normal). Rule Tool flagged a minor configuration item: default alerts not enabled on the SEL-351 Relay (Device communication 250, SEL 351 Breaker Bit Alert 720) â monitoring visibility only.
-Forecast calls for light rain Jun 9â10 with clearing and 77Â°F on Jun 11, supporting improved production midweek.[DONE]</t>
+          <t>All hardware is communicating normally as of Jun 9 at 8:25 AM PDT, and the SMA SC4000 inverter is producing in line with expected output for the prevailing light rain conditions. No active production events.
+Over the last 30 days, the site has performed well with an average EPI near 1.00 and 100% inverter availability. Total production of 1,081 MWh exceeded estimate by 16%. Sampled-inverter PV model losses and tracker losses show nothing notable.
+Meter-to-inverter ratio is 0.99, normal. The rule tool flagged a configuration item: default alerts (device communication, SEL 351 Breaker Bit) are not enabled on the SEL-351 Relay â a monitoring visibility gap only.
+Forecast shows light rain Jun 10, then clearing to 75â79Â°F Jun 11â12, favorable for strong production midweek.[DONE]</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="113" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="98" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>S54613</t>
@@ -774,20 +772,20 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>All 32 inverters online and reporting as of Jun 8 at 10:55 PM EDT, with the site having completed a normal production day (26.2 MWh at the meter, peaking near 3.7 MW around 2 PM). Current conditions are clear and 73Â°F, post-sunset.
-Inverter B19 shows a recurring pattern of zero production during early-to-mid morning hours (roughly 8â11 AM) on Jun 3â6, while peers produced normally â a partial-capability issue worth monitoring on the production and expected chart. Daily impact is minor (&lt;5% site).
-30-day EPI averages 0.89 and inverter availability 97%, pulled down by low-irradiance days May 22â26 and Jun 1â2. Sampled-inverter PV model losses show no major issues.
-Meter-to-inverter ratio is 0.99 (normal). The Jun 6 rule tool communication warning reflects minor inverter uptime gaps with no production correlation.
-Forecast: light to heavy rain Jun 9â11 will reduce output.[DONE]</t>
+          <t>All 32 inverters online and producing as of Jun 9 at 11:26 AM EDT under light rain, consistent with low morning irradiance. No active production event.
+Over the past 30 days, the Energy Performance Index averaged about 0.88, with weather-driven dips on May 23 (0.66), May 26 (0.67), and Jun 1 (0.77).
+Inverter availability averaged 97%, with the lowest day at 76% on May 23. Sampled-inverter PV model losses show modest soiling, downtime, and residual losses â nothing notable.
+Meter-to-inverter ratio is 0.99, normal. The rule tool flagged minor inverter uptime gaps (most at ~98%); no current production correlation.
+Forecast: clear Jun 10 (high 90Â°F), then rain Jun 11â12 with highs near 95Â°F â expect reduced output on the rainy days and possible mild thermal derate.[DONE]</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="107" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="114" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>S54681</t>
@@ -800,15 +798,16 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Site gateway PowerLogger 1000 and Cell Modem (RV50) stopped reporting on Jun 6 at 3:05 PM EDT, so no inverter, meter, or weather telemetry has updated for ~2 days. The meter-to-inverter ratio over the last hours of available data on Jun 6 was ~0.99, indicating inverters were producing normally up to the comms loss. The production chart shows blank values Jun 7â8; actual site production status is unknown until the data logger is restored.
-30-day Energy Performance Index averages 0.97 with inverter availability at 99%. No major losses identified on the sampled inverter.
-Two external fan fault alerts on Inv-5 and Inv-8 from Jun 6 morning; Inv-8 had visibly clipped output (~75 kW vs ~125 kW peers) on Jun 2â5. Meter-to-inverter ratio 0.99 (normal).
-Forecast calls for light rain Jun 9â11 with highs near 82Â°F; expect reduced production.[DONE]</t>
+          <t>Site gateway PowerLogger 1000 and Cell Modem (RV50) stopped reporting on Jun 6 at 3:05 PM EDT, halting all telemetry uploads since. However, inverter production through Jun 6 shows normal output, and the meter-to-inverter ratio of 0.99 over 30 days confirms metering integrity through that date. Current production state after Jun 6 cannot be verified until the data logger is restored.
+No production events identified in the reporting window. Inverter 8 consistently produces ~75 kW vs. ~125 kW peers â a persistent performance issue, not a discrete event.
+30-day EPI averages 0.97; inverter availability 99%. No major losses on the sampled inverter.
+Active alerts include External Fan Errors on Inverters 5 and 8 (Jun 6) and weather station irradiance/temperature invalid flags affecting expected energy inputs.
+Light rain forecast through Jun 12 with mild temperatures; reduced production expected.[DONE]</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
+          <t>2026-06-09 17:54 UTC</t>
         </is>
       </c>
     </row>
@@ -825,20 +824,20 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>All 80 SunGrow inverters and both trackers are communicating as of Jun 8 at 10:56 PM EDT, with the site operating normally through the day. Peak hourly output reached ~9,996 kW around midday, and actual production tracked expected closely at 98%.
-Conditions are clear and 73Â°F after sunset.
-Over the past 30 days, EPI averaged 0.94 and inverter availability averaged 99%. No major losses identified on the sampled inverter; tracker lost energy was zero all week.
-Meter-to-inverter ratio is 0.99, normal. A GameChange Tracker 2.1 E-Stop fault triggered at 10:49 PM with no production impact (post-sunset). The original GameChange Tracker Control unit has been offline since Jun 2024 â monitoring-only. A stale "not responding" alert from Aug 2025 on that same legacy tracker remains open.
-Forecast: light rain Jun 9 and 11, clear Jun 10, with highs to 99Â°F â some heat derating possible Jun 11.[DONE]</t>
+          <t>All 80 SunGrow SG125HV inverters are communicating and producing as of Jun 9 at 11:26 AM EDT, with site output ramping under clear skies (84Â°F, light wind).
+The site is operating normally. Three active alerts are advisory: a stale tracker-comm alert on the original GameChange Tracker Control (Aug 29, 2025), a tracker E-Stop on Tracker Control 2.1 triggered Jun 9 at 9:56 AM, and a Rule Tool summary. Tracker lost energy reads 0 kWh across the last 7 days.
+30-day EPI averages 0.94 with inverter availability at 99%. No major losses identified on the sampled inverter.
+Meter-to-inverter ratio is 0.99 (normal). Rule Tool flags soiling on inverters 22, 39, and 42 (5â6%), a POA sensor configured as fixed-tilt rather than tracking, and tracker configuration gaps worth review.
+Forecast: light rain Jun 10â11, rain Jun 12, highs to 99Â°F â expect reduced output and possible heat derating.[DONE]</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="111" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="94" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>S63837</t>
@@ -851,19 +850,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>All 26 inverters are online and producing as of Jun 8 at 10:56 PM EDT, with the site currently in post-sunset hours. Earlier today, peak hourly output reached about 2.35 MW around midday before variable afternoon production consistent with passing clouds.
-No production events occurred in the reporting period. The 30-day Energy Performance Index averages 0.99 and inverter availability is 100%. Sampled-inverter losses show no notable issues; tracker losses are minor at roughly 40â95 kWh/day.
-Meter-to-inverter ratio is 0.98, normal. The rule tool flags an iPRO security camera upload delay, AE Smart UPS default alert configuration, and three trackers (Position A1 S 22, S 54, S 79) stuck at fixed angles â visibility and tracker positioning items only.
-Forecast is clear with highs of 93â95Â°F through Jun 11; favorable for production with mild temperature derate possible.[DONE]</t>
+          <t>All 24 inverters online and producing as of Jun 9 at 11:27 AM EDT, with clear skies and 84Â°F. Site is operating normally; current-day production is ramping through the morning per the production and expected chart.
+30-day Energy Performance Index averages 0.99 with inverter availability at 100%. Sampled-inverter PV model losses show no notable issues; tracker losses average ~70 kWh/day, minimal.
+Meter-to-inverter ratio is 0.98, normal. Rule tool flags three trackers stuck at fixed angles (A1 S 22, S 54, S 79) and elevated error on A1 S 46 â worth field review but low energy impact. AE Smart UPS default alerts not set.
+Forecast: clear Jun 10â11 with highs 93Â°F, light rain Jun 12 (97Â°F). Favorable production conditions through midweek.[DONE]</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="94" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="86" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>S63838</t>
@@ -876,19 +875,20 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>All 28 inverters are online and communicating as of Jun 8 at 10:56 PM EDT, with sunset reached and no active production events. The site is operating normally.
-30-day Energy Performance Index averages 0.98 with inverter availability at 100%. Meter production totals 659 MWh against 758 MWh estimated (87%). Sampled Inverter 13 PV model losses show only minor age and soiling losses.
-Meter-to-inverter ratio is 0.98, normal. The rule tool flags FlexRack tracker "Position A1 S 16" reading 0 degrees and AE Smart UPS default alerts not set; tracker lost energy is minor (~10â40 kWh/day).
-Forecast is clear with highs of 93â95Â°F through Jun 11. No weather impacts expected, though sustained high temperatures may produce minor thermal derate.[DONE]</t>
+          <t>All 28 inverters and supporting hardware are communicating normally as of Jun 9 at 11:27 AM EDT, with the site producing under clear skies (84Â°F). Morning ramp is tracking expected output closely.
+30-day Energy Performance Index averages 0.97 with inverter availability at 100%. Estimated energy ratio is 87%.
+Sampled-inverter PV model losses show only routine age and soiling. Tracker losses are minor (~10â40 kWh/day).
+Meter-to-inverter ratio is 0.98, normal. Rule tool flags Position A1 S 16 stuck at 0Â° and AE Smart UPS default alerts unset â monitoring items only.
+Forecast is clear Jun 10â11 with highs near 93Â°F, then light rain Jun 12; no expected operational impact.[DONE]</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="127" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="117" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>S63839</t>
@@ -901,20 +901,20 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>All 24 inverters are online and reporting as of Jun 8 at 10:56 PM EDT, with nighttime conditions (clear, 77Â°F) and no production expected.
-Today's daytime output peaked around 2.5 MW mid-morning before variable production consistent with passing clouds; expected energy tracked actual closely.
-30-day Energy Performance Index averaged 0.99 and inverter availability was 100% â site is healthy. Sampled-inverter PV model losses show no notable issues; tracker losses averaged ~40 kWh/day (&lt;0.2% of production).
-Meter-to-inverter ratio is 0.98 â normal. Rule tool flags on the 10/11 String INV groups reflect inverter-group rollups (0% availability) that are contradicted by full inverter production; NCU 1 reports two stuck tracker positions worth monitoring. Inverter 24 shows an energy ratio of 1.10, possibly indicating peer-relative overperformance or model calibration.
-Forecast: light rain Jun 9, then clear with highs 91â95Â°F Jun 10â11 â favorable production with possible mild heat derate.[DONE]</t>
+          <t>All 24 inverters online and producing as of Jun 9 at 11:27 AM EDT, with light rain and reduced irradiance limiting current output. Site weather is mild (86Â°F, 3 mph wind).
+Recent daily production has tracked expected output closely (101% actual/expected over 7 days), confirming normal operations.
+30-day Energy Performance Index averages 0.99 and inverter availability is 100%. Sampled-inverter PV model losses show no notable issues; tracker losses are minor (~20â55 kWh/day).
+Meter-to-inverter ratio is 0.98 â normal. The rule tool flagged 0% availability on the "10 String" and "11 String" inverter groups, but production data confirms these groups are generating normally â a configuration artifact only. NCU 1 reports two trackers stuck at fixed angles (Position A1 S 10 and S 56); worth field verification.
+Forecast: clear and warm Jun 10â11 (highs 93â97Â°F), favorable for production; light rain returns Jun 12.[DONE]</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="118" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="114" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>S63840</t>
@@ -927,19 +927,20 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>All 24 inverters communicating as of Jun 8 at 10:57 PM EDT, with last updates within the past few minutes. Site is post-sunset; today's production tracked expected closely under light rain, peaking around 2.2 MWh in the 11 AM hour before clouds reduced output through the afternoon per the production and expected chart.
-30-day Energy Performance Index averaged 0.96 with inverter availability at 100%. Sampled-inverter PV model losses and tracker losses show no major issues.
-Meter-to-inverter ratio is 0.98, normal. Rule tool flags a POA insolation mismatch of +65% on the Kipp &amp; Zonen SMP-12 (POA) sensor â verify azimuth/tilt configuration, as this can skew expected energy. Also noted: AE Smart UPS default alerts not set, and ION 8650 meter phase current ratio at 100% with near-zero PF (post-sunset artifact).
-Light rain forecast through Jun 11 with highs reaching 90Â°F; expect variable output and possible mild thermal derate.[DONE]</t>
+          <t>All 24 inverters online and reporting as of Jun 9 at 11:27 AM EDT, with light rain (73Â°F) limiting current output. Morning production is tracking expected under overcast conditions per the hourly production and expected chart.
+No production events in the last two weeks. Daily output has varied with weather, with strong days Jun 3â5 (~32 MWh) and weather-limited days Jun 7â8.
+30-day Energy Performance Index averages 0.96 with inverter availability at 100%. Sampled-inverter PV model losses and tracker losses show nothing notable.
+Meter-to-inverter ratio is 1.02, slightly elevated. The rule tool flags a meter phase current/PF imbalance, a POA insolation mismatch of +61% on PY0 (check azimuth/tilt), and low BPOA insolation â review sensor calibration as these affect EPI integrity.
+Forecast: clear Jun 10 (90Â°F) then light rain Jun 11â12; expect strong production Tuesday, reduced midweek.[DONE]</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="103" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="105" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>S64602</t>
@@ -952,19 +953,20 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>All 40 inverters reporting as of Jun 8 at 10:57 PM EDT, with the site producing normally through the day. Peak output reached ~4.8 MW around midday before cloud cover reduced afternoon production, consistent with actual vs expected tracking at 94% over the last 7 days.
-30-day EPI averages 0.93 with inverter availability at 100%. Sampled INVERTER 1 model losses show minor soiling (~1%) and age-related derate; no major losses identified.
-Meter-to-inverter ratio is 0.98, normal. The BPOA pyranometer (PY2) has been offline since Jun 16, 2025 â sensor repair needed but no production impact. Tracker control shows several stuck/misaligned positions with ~118 kWh/day in tracker losses (&lt;0.3% of daily output).
-Forecast: light rain Jun 9 and Jun 11, clear Jun 10 with highs to 97Â°F â minor heat derating possible.[DONE]</t>
+          <t>All 40 inverters communicating as of Jun 9 at 11:27 AM EDT, with the site producing under light rain. Today's production ramped to ~3.8 MW by 10 AM, consistent with overcast conditions.
+30-day Energy Performance Index averages 0.92 with inverter availability at 100%. Sampled inverter shows minor soiling (~1%) and age losses; no major losses identified.
+Meter-to-inverter ratio is 0.98, normal. The BPOA pyranometer (PY2) has been offline since Jun 16, 2025; backup POA sensor remains operational.
+Tracker control (ST0) reports multiple slave positions stuck at 0Â° and ~26Â° average tracker error on three rows, with tracker losses running ~120 kWh/day (&lt;0.3% of site output).
+Forecast calls for light rain and highs of 93â99Â°F through Jun 12; expect continued reduced output with possible thermal derating on the warmer days.[DONE]</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="106" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="98" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>S64603</t>
@@ -977,20 +979,20 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>All 72 inverters are online and communicating as of Jun 8 at 10:57 PM EDT, with the site closing out the day at EPI 1.00 and 78.3 MWh produced against a 79.3 MWh estimate. Peak hourly output reached ~8.9 MW near AC capacity midday.
-Conditions are clear, 75Â°F, with sun down.
-No production events in the last two weeks. Daily EPI averaged 0.96 and inverter availability 99% over 30 days. Sampled-inverter PV model losses show nothing notable; tracker losses averaged ~130 kWh/day.
-Meter-to-inverter ratio is 0.98, normal. Two active tracker alerts flag an e-stop on slave S 54 (ST1) and low state-of-charge on S 25 and S 48; rule tool also notes ST2 average tracker error of 34Â° on S 25 and two slaves stuck at 0Â°. Worth field follow-up but limited energy impact.
-Light rain and highs rising to 99Â°F Jun 9â11 may modestly reduce output.[DONE]</t>
+          <t>All 72 inverters are communicating and operating as of Jun 9 at 11:28 AM EDT under light rain with reduced irradiance. Today's production has ramped through the morning consistent with the overcast conditions.
+A brief mid-morning dip on Jun 5 (EPI 0.81) shows in the PV model losses for the sampled inverter as ~210 kWh of downtime, but daily availability and meter totals remained healthy.
+30-day EPI averages 0.96 with inverter availability at 99%. Sampled soiling loss ~5% is the main detractor.
+Meter-to-inverter ratio is 0.98 (normal). Open tracker alerts on ST1 (not responding since 10:18 AM, low SoC, e-stop) and ST2 (low SoC) should be reviewed; tracker losses remain under 200 kWh/day.
+Forecast is light rain with highs 93â100Â°F through Jun 12; no derating expected.[DONE]</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="94" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="109" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>S65216</t>
@@ -1003,20 +1005,20 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 8 at 8:28 PM PDT, including Inverter 1, the production meter, and weather sensors. The site is producing through light rain today, with cloud-driven variability visible in hourly production versus expected. No production events identified.
-Over the last 30 days, the Energy Performance Index averaged 1.00 and inverter availability was 99%, with a brief dip to 85% on May 28.
-Site production totaled 99% of estimate. No major losses identified in the sampled-inverter model; tracker losses were minimal (~3â28 kWh/day).
-Meter-to-inverter ratio is 0.99, which is normal. No active alerts.
-Forecast shows light rain Jun 9, then clear skies Jun 10â11 with highs reaching 77Â°F, favorable for production.[DONE]</t>
+          <t>All hardware is communicating as of Jun 9 at 8:28 AM PDT, with Inverter 1 producing 2,625 kWh in the 7:00 AM hour. Conditions are clear and cool, supporting normal operations.
+Production was reduced on Jun 8 (10.7 MWh vs. ~28 MWh estimated) and Jun 3 (17.4 MWh), consistent with low irradiance on those days per the PV model. May 28â29 also showed depressed output (~9.8â16.9 MWh) with one availability dip to 85% on May 28; no current impact.
+30-day EPI averages ~0.99 and inverter availability is 99%. Site reached 99% of estimate over 30 days. Sampled-inverter losses and tracker losses (3â28 kWh/day) are minor.
+Meter-to-inverter ratio is 0.99, normal. Rule tool flagged high energy ratio on Jun 8 from low expected output â a mathematical artifact, not a performance issue.
+Forecast is clear with highs rising to 82Â°F by Jun 12, favorable for production.[DONE]</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="118" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="113" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>S65784</t>
@@ -1029,20 +1031,20 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>All 40 inverters are online and reporting fresh telemetry as of Jun 8 at 10:58 PM EDT, with no active alerts. Site is past sunset; conditions are clear and 75Â°F.
-Today's site reached ~4.8 MW peak around midday, with actual production tracking near expected through the day. No production events identified in the last 30 days.
-30-day inverter availability is 100%, and total production is 96% of estimate. The Energy Performance Index averages ~1.17, persistently above 1.1, suggesting a PV model or POA/pyranometer calibration issue worth review. Sampled INVERTER 15 shows no notable losses beyond expected age/soiling.
-Meter-to-inverter ratio is 0.98 (normal). Rule tool flags stuck AC voltage telemetry on all 40 inverters and many tracker positions stuck at 0Â° on TCU 1 and TCU 95-111 â data quality items not impacting production.
-Forecast: light rain Jun 9, heavier rain Jun 10-11 with highs to 97Â°F; expect reduced output.[DONE]</t>
+          <t>All 40 inverters are communicating as of Jun 9 at 11:28 AM EDT, with the site producing through light rain this morning. Today's output is weather-limited (~4.5 MWh by 11 AM), consistent with overcast conditions.
+30-day inverter availability is 100%, and production reached 94% of estimate (1,262 MWh actual vs 1,328 MWh estimated).
+The Energy Performance Index averages 1.17, persistently above 1.1, suggesting a PV model or pyranometer calibration issue rather than a performance problem.
+Meter-to-inverter ratio is 0.98 (normal). The rule tool flags stuck AC voltage telemetry on all 40 inverters, several tracker positions stuck at 0Â°, and ~39Â° average tracker error on TCU 96â108 â monitoring/data quality flags with no production correlation (tracker losses &lt;3 kWh/day).
+Forecast calls for rain and highs to 99Â°F through Jun 12; expect reduced output and possible thermal derating.[DONE]</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="100" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="106" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>S65785</t>
@@ -1055,19 +1057,19 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>All 24 inverters online and producing normally as of Jun 8 at 10:58 PM EDT, with the site clear at 64Â°F. Today's production reached 31,269 kWh with multiple hours at full 3 MW AC capacity.
-30-day EPI averages 0.96 and inverter availability is 100%. Site produced 811.6 MWh versus 789.9 MWh estimate (103%). Sampled-inverter PV losses and tracker losses (~7 kWh/day) are minor.
-Meter-to-inverter ratio is 0.98, normal. The rule tool flags soiling losses of 9â11% on Inverters 3, 8, and 17, and a 33Â° average tracker error on TCU 87 tied to an Apr 20 tracker fault alert; worth a field check but no material production impact. The 13 String/12 String 0% availability flags are an inverter-group configuration artifact.
-Clear Jun 9 (88Â°F); light rain Jun 10 and rain Jun 11 will reduce output.[DONE]</t>
+          <t>All 24 inverters online and producing normally as of Jun 9 at 11:28 AM EDT, with clear skies and 79Â°F supporting strong morning output near 3 MW AC capacity per the production and expected chart.
+30-day EPI averages 0.96 with inverter availability at 100%. 30-day production totaled 814 MWh, 103% of estimate. Sampled-inverter PV model losses show no major issues; tracker losses are minimal (~7 kWh/day).
+Meter-to-inverter ratio is 0.98, normal. The rule tool flags excessive soiling on INV-3, 8, and 17 (~9â11%) and a tracker position error of 33Â° on TCU 87 â worth monitoring. Active alerts include a UPS battery over-temperature (Jun 9 at 9:14 AM) and the standing tracker TCU 87 blocked-axis warning from Apr 20.
+Forecast calls for light rain Jun 10â12 with highs to 97Â°F; expect reduced output and possible mild thermal derating.[DONE]</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="114" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="116" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>S65786</t>
@@ -1080,20 +1082,20 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>All 16 inverters communicating as of Jun 8 at 10:58 PM EDT, with last uploads within the past 3 minutes. Site is past sunset; daytime peak today reached ~2.0 MW around midday, tracking expected output well.
-Conditions are clear at 75Â°F with light winds; nighttime, so no production impact.
-Energy Performance Index averaged 0.91 over 30 days, with inverter availability at 100%. Production totaled 479 MWh vs. 552 MWh estimated (87%), reflecting variable weather. Sampled-inverter PV model losses and tracker losses (~5 kWh/day) are minor.
-Meter-to-inverter ratio is 0.98, normal. Rule tool notes minor availability dips (~98%) on Inverters 1, 3, 6, 11, 15, a stuck Tracker Position TCU 24 at 0Â°, and module-vs-ambient temperature flag â monitoring items only.
-Forecast calls for light rain and highs 88â99Â°F Jun 9â11; expect reduced output and possible temperature derating on the hottest day.[DONE]</t>
+          <t>All 16 inverters online and producing as of Jun 9 at 11:29 AM EDT under light rain and overcast skies, which is suppressing today's output (morning peak ~793 kW at 10 AM).
+No production events in the reporting period. Recent clear days (Jun 3â5) reached the 2,000 kW AC cap with actual/expected at 96%.
+30-day Energy Performance Index averages 0.91 and inverter availability is 99%. Sampled-inverter PV model shows no major losses; tracker losses are negligible (~5 kWh/day).
+Meter-to-inverter ratio is 0.98 (normal). A UPS Battery Over Temperature warning triggered Jun 9 at 11:18 AM â monitoring infrastructure only, no production impact. Rule tool flags Tracker Position TCU 24 stuck at 0Â° and back-of-module temp below ambient; worth verifying sensor and tracker calibration.
+Forecast: light rain and highs 91â99Â°F through Jun 12; expect continued weather-driven variability with possible heat derating midweek.[DONE]</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="115" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="113" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>S65787</t>
@@ -1106,20 +1108,20 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>All 80 inverters are online and communicating as of Jun 8 at 10:58 PM EDT, with the site offline for the night. Today's site produced 86,013 kWh against 88,152 kWh estimated, with a peak hourly output near 9.7 MW mid-morning before variable afternoon output consistent with passing clouds.
-No production events occurred in the reporting period.
-30-day EPI averages 0.97 and inverter availability is 99%. Sampled INV 21 PV model shows no major losses beyond routine age and soiling.
-Meter-to-inverter ratio is 0.98 (normal). A stale 90Â°C transformer liquid temp fault from May 17 on XFMR IO2 remains unresolved with no production correlation. Multiple trackers (TCU 39, 72, 161, 6, 16) report stuck at 0Â°, with ~46 kWh tracker loss today â minor impact worth field verification.
-Forecast calls for light rain and highs 88â99Â°F through Jun 11; expect reduced output and possible heat derating on the warmest day.[DONE]</t>
+          <t>All 80 inverters online and producing as of Jun 9 at 11:29 AM EDT, with the site ramping under light rain (88Â°F). Today's production is tracking the expected output curve through mid-morning.
+Recent peak days (Jun 3â5) hit ~112 MWh against the ~88 MWh estimate, confirming healthy plant output.
+30-day EPI averages 0.97 and inverter availability is 99%, with a brief dip to 72% on May 30. Sampled INV 25 shows ~7% soiling loss as the main recoverable loss; tracker losses are minor (~50 kWh/day).
+Meter-to-inverter ratio is 0.98 (normal). A May 17 transformer 90Â°C liquid temp fault (IO2) remains unresolved but shows no production correlation. Rule tool flags several stuck/misaligned trackers (TCU 39, 72, 161, 6, 16) and a POA pyranometer reading ~72% high â worth review for EPI integrity.
+Forecast: clear Jun 10, then light rain and highs near 99Â°F Jun 11â12; watch for thermal derate.[DONE]</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="111" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="98" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>S65788</t>
@@ -1132,16 +1134,16 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Site is in nighttime hours as of Jun 8 at 10:59 PM EDT; all 40 inverters, meter, data logger, and weather sensors last reported within the past few minutes. INVERTER 2.6 remains in an outage since May 20, last producing data per the rule tool (~1.1 MWh lost over 19 days at ~125 kW nameplate, ~60 kWh/day).
-Today's production reached 32.6 MWh with a midday peak near 4.9 MW before clouds reduced afternoon output, consistent with the day's EPI of 0.86.
-30-day EPI averages 0.90 with inverter availability at 97%, both pulled down by INV 2.6. Sampled INV 1.1 shows no notable losses beyond curtailment artifacts.
-Meter-to-inverter ratio is 0.98 (normal). Rule tool flags 10 trackers with elevated positioning error (3 stuck at 0Â°), but tracker losses remain under 20 kWh/day.
-Forecast: light rain Jun 9 and Jun 11, clear Jun 10 with highs reaching 99Â°F â monitor for heat derating.[DONE]</t>
+          <t>INVERTER 2.6 has been offline since May 20 at 6:17 PM EDT, confirmed by the meter-to-inverter ratio of 0.98 (normal range, indicating the unit is not producing).
+This is an outage of ~125 kW (~2.5% of site capacity), ~14 MWh lost over ~20 days at ~0.7 MWh/day expected. The remaining 39 inverters are producing normally under clear skies at 82Â°F.
+30-day EPI averages 0.88 and inverter availability 98%, both consistent with the single-inverter outage. Tracker losses are minor (~17 kWh/day).
+Rule Tool flags multiple trackers stuck at 0Â° (TCU 49, 131, 153) and elevated tracker errors on TCUs 1, 4, 78, 151 â worth field verification but low energy impact.
+Forecast: clear Jun 10, then light rain/rain Jun 11â12 with highs near 99Â°F. Heat may cause mild inverter derating.[DONE]</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
+          <t>2026-06-09 17:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1158,20 +1160,20 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Site is producing but with multiple inverter issues as of Jun 8 at 10:59 PM EDT. Meter-to-inverter ratio today is ~0.36 (5,560+6,300 kWh meter vs 15,619 kWh inverter), well below 0.92, indicating meter data is unreliable; inverter telemetry is authoritative.
-INVERTER 4 has been at 0 kW all day with a Solectria fault alert triggered at 5:02 PM â classify as a forced outage (~200 kW, ~1 MWh/day at current output). INVERTERS 7, 9, 13, 17, 23, 34, 35 remain non-communicating (stale 7â63 days); peer inverters produced normally today, so production chart confirms these as communication losses with visibility risk, not confirmed outages.
-30-day meter production is 717.6 MWh vs 1,775 MWh estimate (40%); meter gaps drive most of this shortfall. EPI and availability are unavailable.
-All weather sensors (POA, GHI, BPOA, ambient) and METER 1 stale since Apr 27âMay 13 â expected energy cannot be calculated. Trackers show ~33â40Â° average position error per rule tool; tracker lost energy chart shows 0 kWh.
-Light rain now; rain forecast through Jun 11 with mild temps â modestly reduced production expected.[DONE]</t>
+          <t>Site is producing but with multiple equipment issues. As of Jun 9 at 11:30 AM EDT, 33 of 35 inverters are reporting current production. INV-7 (last upload Jun 2) and INV-9 (last upload Jun 2) show meter-to-inverter ratio near 1.00 today, consistent with confirmed outages rather than comm loss. INV-17, INV-23, INV-35, INV-13, INV-34 have been offline 7-63 days â sustained production loss.
+Approximately 7 inverters (~20% of capacity) currently offline. Estimated loss ~12 MWh/week (~250 kW affected, ~7 hrs/day production). New urgent faults today on INV-1 (External Fan Damaged), INV-4, INV-14 (Hardware self test failure) require attention via active alerts.
+30-day site production totals 721 MWh vs 1,782 MWh estimate (40%), reflecting widespread inverter unavailability and overcast periods.
+METER - PRODUCTION 1 not responding since May 13; meter-to-inverter ratio currently elevated at 1.08. Weather station and pyranometers offline since May 13 â POA/GHI/BPOA invalid, affecting EPI calculation. Tracker Control 1 and 2 reporting average ~37Â° position errors.
+Light rain today through Jun 12; clear Jun 11.[DONE]</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="103" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="116" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>S66000</t>
@@ -1184,20 +1186,20 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 8 at 7:46 PM PDT, with INVERTER 1 producing in line with expected output through the day under light rain (54Â°F).
-Today's production is tracking low due to overcast/rain conditions, consistent with weather rather than equipment issues.
-Over the last 30 days, the site is healthy: EPI averaged 1.10, inverter availability 100%, and actual vs. estimate at 123%. The persistently elevated EPI suggests a PV model or POA sensor calibration issue worth reviewing. Tracker losses are negligible (&lt;20 kWh/day).
-Meter-to-inverter ratio is 0.99 (normal). The rule tool flags the POA pyranometer as configured for a tracker but appearing fixed-tilt â recommend verification, as this may be inflating EPI.
-Forecast: light rain Jun 9â10, clearing Jun 11 (75Â°F) for improved production.[DONE]</t>
+          <t>Inverter 1 is online and producing, with the datalogger and meter reporting fresh telemetry as of 8:30 AM PDT. Current conditions are light rain at 52Â°F, consistent with the subdued morning ramp seen in the production and expected chart.
+No production events identified in the last 2 weeks. June 8 was a low-output day (~5.8 MWh) consistent with overcast conditions, with actual tracking expected.
+The 30-day Energy Performance Index averages 1.09, slightly elevated and worth monitoring for possible PV model or POA sensor calibration drift. Inverter availability is 100%. Tracker losses are negligible (&lt;13 kWh/day).
+Meter-to-inverter ratio is 0.99, normal. The rule tool flags the POA pyranometer as configured fixed-tilt on a tracker site â recommend reviewing sensor configuration as this may explain the elevated EPI.
+Forecast clears to 75â77Â°F Jun 11â12, supporting strong production after light rain Jun 10.[DONE]</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="102" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="99" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>S66001</t>
@@ -1210,20 +1212,20 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Inverter 1 is online and producing, with all hardware reporting as of Jun 8 at 7:59 PM PDT. Today's output is suppressed by light rain, with hourly production peaking near 1.2 MW midday against expected output tracking actual closely.
-No production events in the last two weeks. Daily output has varied with weather but expected energy tracks actual on a daily basis.
-30-day Energy Performance Index averages 1.02 and inverter availability is 100%. Sampled PV model losses show no major issues; tracker losses are minimal.
-Meter-to-inverter ratio is 0.99, normal. A rule tool weather station "temperature too high" flag is open with no production correlation â monitoring only.
-Forecast: light rain Jun 9â10 (continued reduced output), clearing Jun 11 with highs near 77Â°F â good production expected.[DONE]</t>
+          <t>Inverter 1 is online and producing, with the hardware fleet reporting fresh telemetry as of Jun 9 at 8:30 AM PDT. Morning output is tracking expected under light rain (486 kWh at 7:00 AM vs. 418 kWh expected per the production and expected chart).
+Jun 8 was a heavy overcast day (6,655 kWh on the meter), consistent with weather rather than an equipment issue.
+30-day EPI averages 1.02 and inverter availability is 100%. Production totaled 832 MWh against a 728 MWh estimate (114%). No notable losses on the PV model chart; tracker losses are minimal.
+Meter-to-inverter ratio is 0.99, normal. The rule tool flagged a weather station high-temperature data check; no production impact.
+Light rain today, then clearing Jun 11â12 with highs in the upper 70s â favorable for production.[DONE]</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="118" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="130" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>S66930</t>
@@ -1236,20 +1238,20 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Site time is after sunset (Jun 8 at 10:59 PM EDT), so inverters are not expected to produce. Inverter - 01.02 has been offline since May 27 at 3:29 AM per the device heartbeat alert; meter-to-inverter ratio context confirms a sustained outage on that single 125 kW unit (~2.5% of capacity). Estimated loss ~14 MWh over 12 days (~1.2 MWh/day expected for the sampled unit per the PV model losses).
-Today's production tracked expected through midday then fell off sharply after 1 PM under variable cloud cover; daily availability dropped to 77%.
-30-day site availability is 96%. Production meter reports zero â meter-to-inverter ratio is unusable; use inverter totals.
-Monitoring flags: SEL 735 meter not reporting energy, weather station POA insolation +25%, and multiple NCU 1/2 tracker motor current anomalies per the rule tool.
-Forecast: light rain and highs 88â99Â°F Jun 9â11; expect variable output and possible heat derating.[DONE]</t>
+          <t>Elk Solar is operating at partial capability as of Jun 9 at 11:30 AM EDT. The production meter has been offline for the full 30-day window (no meter data), so inverter telemetry is authoritative.
+Inverters 01.02 and 01.15 have been offline since May 27, and inverters 01.08â01.14 dropped offline on Jun 8 â collectively ~9 inverters (~21% of site capacity) in an outage. Estimated loss ~17 MWh (Block 1 inverters offline, ~750 kWh/day per sampled inverter, 01.02 down ~13 days plus seven units down ~2 days). Weather is light rain, limiting today's irradiance.
+30-day EPI is unavailable (meter down); inverter production totals 967 MWh vs. 1,308 MWh estimate (74%). Inverter availability averaged 95%, dropping to 77% on Jun 8.
+Monitoring flags: production meter offline (meter-to-inverter ratio not computable), multiple tracker motor current and position anomalies on NCU 1/NCU 2, weather station POA +19% vs. peers, and inverter 01.15 telemetry stuck at zero.
+Forecast: clear Jun 10, then rain Jun 11â12 with highs to 99Â°F.[DONE]</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="110" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>S68112</t>
@@ -1262,19 +1264,20 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Inverter 1 is online and producing, with the most recent hardware update at 7:53 PM PDT on Jun 8. Today's production has been limited by light rain, with a peak hourly output near 1.49 MWh during the afternoon per the production and expected chart. No production events identified.
-The 30-day Energy Performance Index averages about 1.07, persistently above 1.0, suggesting a PV model or pyranometer calibration issue rather than a plant problem. Inverter availability is 100%. Tracker losses have been minimal (under 60 kWh/day) per the tracker chart.
-Meter-to-inverter ratio is 0.99, normal. The rule tool flags high energy ratios and a POA pyranometer reading about 55% above the other sensors â recommend verifying POA tilt/azimuth and BPOA calibration.
-Forecast: light rain Jun 9â10, then clear and warm Jun 11 (77Â°F) â good production conditions returning midweek.[DONE]</t>
+          <t>All hardware is communicating as of Jun 9 at 8:30 AM PDT, with Inverter 1 producing 1,317 kWh in the 7 AM hour under light rain. Current conditions are overcast with light rain, consistent with the reduced output seen on Jun 8 and the morning of Jun 9.
+No production events identified in the last two weeks. Day-to-day variability on the production chart tracks weather, not equipment issues.
+30-day inverter availability is 100%. The 30-day average Energy Performance Index is 1.06, persistently above 1.0, suggesting a PV model or pyranometer calibration issue rather than a performance problem.
+Meter-to-inverter ratio is 0.99, normal. The rule tool flags high energy ratio on the meter and inverter, BPOA insolation low, and POA insolation +55% above other sensors â recommend reviewing POA tilt/azimuth configuration and BPOA sensor.
+Forecast: light rain Jun 10, then clear skies and warming highs (75â79Â°F) Jun 11â12, favorable for production.[DONE]</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="97" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="104" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>S68113</t>
@@ -1287,19 +1290,20 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 8 at 7:59 PM PDT, with the inverter, meter, and weather sensors reporting current data. The site is producing under light rain, with today's meter production at 8,775 kWh against a 24,550 kWh estimate, consistent with overcast conditions.
-Over the last 30 days, the site averaged a 0.99 Energy Performance Index and 100% inverter availability, with total production 107% of estimate. No major PV model losses identified beyond normal age and inverter losses; tracker losses are negligible.
-Meter-to-inverter ratio is 0.99, which is normal. No active alerts and the rule tool reports all tests passed.
-Light rain continues through Jun 10, with clear skies and a high of 75Â°F forecast Jun 11, which should support strong production.[DONE]</t>
+          <t>All hardware is communicating as of Jun 9 at 8:29 AM PDT, with Inverter 1 producing in line with expected output through the morning under light rain.
+Recent daily production has been variable due to cloud cover, with low output on Jun 8 (8.8 MWh) and Jun 5 (16.3 MWh), but actual vs. expected tracking remains close, indicating normal weather-driven variation rather than a performance issue.
+30-day Energy Performance Index averages 0.99 and inverter availability is 100%. Total production of 758 MWh exceeds the 710 MWh estimate (107%). No major sampled-inverter or tracker losses identified.
+Meter-to-inverter ratio is 0.99, normal. No active alerts and the rule tool reports all tests passing.
+Forecast shows light rain Jun 10 followed by clear, warm conditions Jun 11â12 (highs 75â77Â°F), favorable for production.[DONE]</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="115" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="119" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>S70532</t>
@@ -1312,20 +1316,21 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>All 40 inverters online and producing normally as of Jun 8 at 11:00 PM EDT, with the site approaching nightfall under clear skies (70Â°F).
-A site-wide grid outage occurred Jun 3â4, with all inverters offline and meter production at zero. Production resumed Jun 5 at normal levels. Estimated loss ~83 MWh (2 days, ~42 MWh/day estimated, 100% capacity). A similar one-day production drop occurred May 17 (EPI 0.06).
-30-day EPI averages ~1.00 on producing days; availability 93%, dragged by the Jun 3â4 outage. Tracker losses ~28 kWh/day are negligible.
-Meter-to-inverter ratio 0.98 (normal). Rule tool flags Tracker Controller 1 comm loss since Jun 3 and a TCU 33 motor overcurrent warning on Tracker Controller 2 â visibility/positioning flags only. A transformer vacuum fault alert from Jun 2 remains open.
-Forecast: light rain Jun 9â11 with highs to 97Â°F; expect reduced output and possible heat derating.[DONE]</t>
+          <t>All 40 inverters are online and producing, with light rain limiting current output to ~1.8 MW around 10 AM EDT. Tracker Controller 1 has been offline since Jun 3 at 7:25 AM, but tracker energy losses are minimal (~0.6 kWh on Jun 9 per the tracker lost energy chart).
+A site-wide outage occurred Jun 3â4, with meter and inverter production at ~0 kWh and availability at 0% both days. Estimated loss ~83 MWh (2 days, ~42 MWh/day expected, full site). Production resumed Jun 5.
+A second multi-day shortfall Jun 21â24 cut meter production sharply (~7â30 MWh/day vs ~40 MWh expected), with no clear root cause in available data.
+30-day EPI averages ~0.98 excluding outage days; availability 93%. Meter-to-inverter ratio 0.98 â normal.
+Tracker Controller 1 comm loss and two transformer vacuum faults remain active alerts for visibility.
+Forecast: rain through Jun 12 with highs to 97Â°F; expect reduced output and possible inverter derating.[DONE]</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="108" customHeight="1">
+          <t>2026-06-09 17:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="97" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>S70645</t>
@@ -1338,42 +1343,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>INVERTER A20 (125 kW, ~2.5% of site capacity) has been offline since Jun 5 following a grid overvoltage fault on Jun 8 at 3:10 PM EDT, followed by a device communication loss at 3:39 PM. Meter-to-inverter ratio confirms a true outage, not just comm loss. Estimated loss ~4.2 MWh (4 days, ~1.05 MWh/day expected per PV model). The remaining 39 inverters are online and producing in line with peers as of 11:00 PM.
-No other production events in the past two weeks. Brief A20 dropouts also occurred May 26â28 and Jun 4, contributing to the availability dip.
-30-day EPI averages 0.97 and inverter availability 99%. Site totals 1,291 MWh against 1,270 MWh estimated (102%).
-Meter-to-inverter ratio 0.97 (normal). Rule tool flags on A20 align with the confirmed outage above.
-Clear tonight; light rain and highs 86â99Â°F Jun 9â11 may modestly reduce output.[DONE]</t>
+          <t>INVERTER A20 (125 kW) has been offline since Jun 5 â the meter-to-inverter ratio of 0.97 over 30 days confirms a true outage, not a comm loss.
+A grid overvoltage fault triggered 21 times in 24 hours, followed by a device communication alert on Jun 8 at 3:39 PM EST, classifies this as a forced outage. The remaining 39 inverters are producing normally.
+Estimated loss: ~4.3 MWh (5 days Ã ~860 kWh/day downtime per PV model losses for the sampled A20).
+30-day EPI averages 0.97 and inverter availability 99%; production tracks estimate at 101%. Tracker losses are minor (~17â27 kWh/day).
+Rule tool flags for A20 (0% availability, downtime loss) align with the confirmed outage.
+Weather: clear today (79Â°F), with light-to-heavy rain Jun 11â12 likely reducing output.[DONE]</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 04:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="133" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>S55935</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Manuel Lawrence Dairy</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Site status cannot be fully assessed at this time. Hardware inventory, production charts, availability, and performance index data were all unavailable for retrieval.
-Without inverter telemetry or meter data, current operational state, the meter-to-inverter ratio, and 30-day performance metrics cannot be confirmed.
-The rule tool reports 0% availability across all inverters and flags invalid module temperature and irradiance from the IMT Ref. Cell, plus an inability to calculate energy ratio or PV losses for all 15 CPS SCA 60KTL-DO inverters. These findings are consistent with a broader data retrieval issue rather than a confirmed field event, and should be re-validated once telemetry is restored. A weather station sensor check is also warranted given the invalid irradiance and module temperature readings.
-No active alerts are present.
-Weather is currently clear at 79Â°F, with a clear and warming forecast through Jun 11 reaching 106Â°F. High temperatures late in the forecast window may cause some inverter thermal derating during peak hours.[DONE]</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09 04:15 UTC</t>
+          <t>2026-06-09 17:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1450,7 +1430,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1460,7 +1440,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -1487,7 +1467,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1524,7 +1504,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -1534,7 +1514,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1613,7 +1593,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -1672,7 +1652,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1719,7 +1699,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1756,7 +1736,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1857,7 +1837,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1867,7 +1847,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2079,7 +2059,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2089,7 +2069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2116,7 +2096,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2237,7 +2217,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2311,7 +2291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2348,7 +2328,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -2385,7 +2365,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2449,7 +2429,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2459,7 +2439,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2523,7 +2503,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2570,7 +2550,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2690,43 +2670,6 @@
         </is>
       </c>
       <c r="G35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>S55935</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Manuel Lawrence Dairy</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/ae_ai_summaries.xlsx
+++ b/ae_ai_summaries.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="101" customHeight="1">
+    <row r="2" ht="98" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>S40834</t>
@@ -489,20 +489,20 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>All 11 Solectria PVI 28TL inverters online and producing normally as of Jun 9 at 11:22 AM EDT, with the meter, weather station, and gateway all reporting within the last few minutes.
-Current conditions are light rain at 75Â°F, consistent with today's lower production trend and reduced irradiance.
-The 30-day Energy Performance Index averages 0.87 with inverter availability at 100%. Sampled-inverter PV model losses are dominated by DC/AC age (~5% each) and a 7% residual, consistent with the EPI gap.
-Meter-to-inverter ratio is 0.97, normal. The Weather Station (Standard) ambient temperature is stuck at -20.2Â°F per the rule tool; this affects expected-energy modeling and should be reviewed.
-Forecast is light rain with highs 88â91Â°F through Jun 12 â expect continued variable, reduced output.[DONE]</t>
+          <t>All 11 Solectria PVI 28TL inverters, both meters, weather stations, and the gateway are communicating as of Jun 9 at 8:02 PM EDT. Today's production was limited by light rain, with peak hourly output near midday around 200 kWh site-wide.
+Over the last 30 days, the site averaged an Energy Performance Index of 0.88 with 100% inverter availability. 30-day production reached 92% of estimate.
+Sampled inverter losses show DC/AC age losses near 5% each and residual loss around 7%, consistent with a maturing system.
+Meter-to-inverter ratio is 0.97, which is normal. One stale Info-level rule tool alert from Jul 2025 remains open with no production correlation.
+Forecast calls for rain and light rain Jun 10â12 with highs 82â88Â°F; expect continued weather-limited output.[DONE]</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="95" customHeight="1">
+          <t>2026-06-10 00:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>S40835</t>
@@ -515,21 +515,21 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Inverter 1 has been offline since Apr 6 at 11:01 AM EDT (last upload Apr 6 at 10:57 AM). The meter-to-inverter ratio of 0.97 over 30 days confirms a true outage, not a communication loss.
-The other 19 inverters are online and producing in line with expected output under light rain conditions (75Â°F).
-Inverter 1 outage: ~36 kW offline (~5% of site), ~64 days, ~13 MWh lost (~200 kWh/day expected per PV model for the sampled inverter).
-30-day EPI averages 0.92 and availability holds at 95%, both reflecting the Inverter 1 outage.
-Meter-to-inverter ratio is 0.97 (normal). Rule tool also flags Inverter 12 with 29% excessive residual loss â worth monitoring.
-Light rain forecast through Jun 12 with highs 88â91Â°F; modest production impact expected.[DONE]</t>
+          <t>Solectria Inverter - 1 has been offline since Apr 6 at 10:57 AM EDT, last upload confirms ~64 days down. Meter-to-inverter ratio today is ~1.06 â consistent with 1 of 20 inverters not producing, confirming an outage rather than comm loss.
+The remaining 19 inverters are producing today, with site output tracking expected energy under light rain (73Â°F). Inverter 12 shows ~29% residual loss versus peers â a persistent underperformance worth field review.
+Estimated loss from Inverter - 1: ~12 MWh over 64 days (~5% capacity, ~200 kWh/day per PV model losses for the sampled inverter).
+30-day EPI averages 0.92; availability holds at 95%, reflecting the single offline inverter.
+Meter-to-inverter ratio is 0.97 (30-day) â normal. An active production meter alert flags a current mismatch (A/B/C phases) on the Main Elkor meter as of today â monitoring flag for CT/wiring review.
+Forecast: rain and light rain through Jun 12, highs 82â88Â°F. Expect reduced output on heavy-rain hours.[DONE]</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="97" customHeight="1">
+          <t>2026-06-10 00:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="105" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>S40836</t>
@@ -542,20 +542,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>All 13 Solectria 28kW inverters online and producing as of Jun 9 at 11:22 AM EDT under light rain, with site output tracking expected energy closely this morning.
-No production events in the last two weeks. Daily output has varied with weather, including low-irradiance days on May 20â22 and May 24.
-30-day Energy Performance Index averages 0.88 with inverter availability at 100%. Sampled-inverter PV model losses show DC/AC age (~5% each) and ~10% residual; no snow or downtime losses.
-Meter-to-inverter ratio is 0.97 (normal). Rule tool flags Weather Station 2 module temperature stuck at -40Â°F â sensor needs review as it may affect expected energy modeling.
-Forecast calls for light rain and highs of 86â90Â°F through Jun 12; expect reduced but normal output.[DONE]</t>
+          <t>All 13 Solectria 28kW inverters online and producing as of Jun 9 at 8:02 PM EDT, with the site in light rain and near sunset. Recent production tracks reduced expected output under cloudy conditions, with no outages observed.
+30-day Energy Performance Index averages 0.88 and inverter availability is 100%. Site produced 53.0 MWh against 58.1 MWh estimate (91%) per the production meter. Sampled-inverter PV model losses show DC/AC age (~5% each) and ~10% residual; no major events identified.
+Meter-to-inverter ratio is 0.97, normal. Rule tool flags Weather Station 2 (GHI) module temperature stuck at -40Â°F â sensor needs attention but does not affect expected energy (Weather Station 1 drives the model).
+Forecast calls for light rain and highs of 82â86Â°F through Jun 12; expect continued reduced output under cloud cover.[DONE]</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="110" customHeight="1">
+          <t>2026-06-10 00:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="106" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>S44485</t>
@@ -568,19 +567,20 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>All 66 inverters online and producing normally as of Jun 9 at 11:24 AM EDT, with light rain and overcast conditions reducing today's output as expected.
-Site is healthy. The 30-day Energy Performance Index averages 1.05, and inverter availability is 100% over the last 7 days (30-day average 99.8%). Production totaled 838 MWh, 107% of estimate. No major losses identified on the sampled inverter.
-Meter-to-inverter ratio is 1.00, normal. The rule tool flags high energy ratios (1.10â1.14) on many inverters and both production meters, suggesting possible PV model or weather station calibration drift worth reviewing. The KYZ Pulse Meter shows 0% availability per the rule tool; verify whether this device is in service.
-Forecast calls for light rain and showers through Jun 12 with highs 73â81Â°F, so reduced output is expected to continue near-term before clearing.[DONE]</t>
+          <t>All 66 inverters online and producing normally as of Jun 9 at 8:04 PM EDT, with site output tracking expected through the day on production vs. expected. Current conditions are light rain at 70Â°F.
+30-day Energy Performance Index averages 1.05, with several days in the 1.11â1.16 range suggesting possible PV model or POA sensor calibration drift worth review.
+Inverter availability is 100%. Sampled-inverter PV model losses show no notable issues beyond normal age and inverter losses.
+Meter-to-inverter ratio is 1.00, normal. Two active warnings flag current mismatch on Elkor Production Meters Site 1 and Site 2 (started Jun 9 at 7:41 PM and 7:44 PM); worth monitoring for CT or wiring issue though totals remain consistent with inverters.
+Forecast is light rain through Jun 12 with highs 73â81Â°F, expect reduced but normal production.[DONE]</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="104" customHeight="1">
+          <t>2026-06-10 00:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="109" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>S44566</t>
@@ -593,19 +593,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>All 27 Chint SCA60KTL inverters are online and reporting as of Jun 9 at 11:24 AM EDT, with the site producing normally under light rain. Today's production is tracking expected output through the morning given overcast conditions.
-30-day Energy Performance Index averages near 1.10 on normal-insolation days, and inverter availability is 94%, pulled down by reduced availability May 27â29. Sampled-inverter losses show no notable issues outside that window.
-Meter-to-inverter ratio is 0.99, normal. The rule tool flags high energy ratios on 6 inverters and low diffuse shade factors site-wide â consistent with the elevated EPI, suggesting a PV model or POA sensor calibration review is warranted.
-Forecast calls for light rain and rain through Jun 12 with mild temperatures (61â82Â°F); expect reduced but normal production.[DONE]</t>
+          <t>All 27 inverters are online and producing as of Jun 9 at 8:04 PM EDT, with light rain and 72Â°F at site. Today's peak hourly output reached ~1.6 MW around midday, consistent with overcast conditions.
+The site is healthy. 30-day EPI averages ~1.10, and inverter availability is 94%, pulled down by reduced availability May 27â29 that has since fully recovered. 30-day production totaled 320 MWh vs. 334 MWh estimate (96%).
+Meter-to-inverter ratio is 0.99, normal. The persistently elevated EPI (~1.10) and large negative residual loss on the sampled inverter suggest a PV model or POA sensor calibration issue worth review, echoed by the rule tool's high energy ratio flags on 19 inverters and low diffuse shade factor configuration warnings.
+Forecast is light rain with highs 77â82Â°F through Jun 12 â reduced but normal production expected, no equipment risk.[DONE]</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="112" customHeight="1">
+          <t>2026-06-10 00:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="105" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>S44882</t>
@@ -618,20 +618,19 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Inverter 20 has been offline since May 31, classified as a forced outage (Insulation Resistance Low / IsolationErr fault). The remaining 26 inverters are producing normally as of Jun 9 at 11:25 AM EDT under clear skies, 73Â°F.
-Impact to date: ~3.5 MWh lost (~10 days, ~1/27 of capacity, ~390 kWh/day per PV model losses for the sampled inverter 20). Site availability has held at 96% since the trip.
-30-day production totaled 286 MWh (113% of estimate). EPI averaged 1.18, persistently above 1.1 across all days â this suggests a PV model or weather station calibration issue worth review.
-Meter-to-inverter ratio is 0.99, normal. Rule tool flags high energy ratio and excessive negative residual losses across most inverters, consistent with the EPI calibration finding.
-Forecast: light rain Jun 10â12 with highs reaching 90Â°F by Jun 12; expect reduced output and possible heat derating.[DONE]</t>
+          <t>Inverter 20 has been offline since May 30, confirmed by an Insulation Resistance Low (IsolationErr) fault and stuck-at-zero AC telemetry. Classified as a forced outage affecting ~73 kW (~3.7% of site capacity), with ~2.3 MWh lost over 11 days (~210 kWh/day expected per the PV model losses for the sampled inverter). All other 26 inverters are online and producing in line with peers as of Jun 9 at 8:03 PM EDT.
+30-day EPI averages 1.18 and inverter availability is 96%, the latter dragged by INV-20. Sustained EPI above 1.1 and rule tool high-energy-ratio flags across all inverters suggest a PV model or weather station calibration issue.
+Meter-to-inverter ratio is 0.99 (normal). Default alerts not set on the Elkor meter.
+Currently clear, 72Â°F. Light rain forecast Jun 10â11, rain Jun 12; modest production reductions expected.[DONE]</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="112" customHeight="1">
+          <t>2026-06-10 00:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="125" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>S51957</t>
@@ -644,20 +643,21 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>All three CPS SCA60KTL inverters are online and producing as of Jun 9 at 9:31 AM EDT, with the data logger reporting at 11:24 AM. Current conditions are clear and 75Â°F.
-However, the site is materially underperforming. The Energy Performance Index has averaged roughly 0.41 over 30 days, with actual production at 49% of expected over the last 7 days. All three inverters show energy ratios near 0.45â0.49 in the rule tool, indicating a site-wide shortfall rather than a single-inverter event.
-PV model losses on the sampled Inverter-1 attribute the gap to large DC/AC age losses (~85%) and ~58% residual losses, with no snow or downtime â suggesting a model calibration concern or sustained derate worth investigating.
-Inverter availability is 100% recently; meter-to-inverter ratio is 1.00 (normal).
-Light rain and highs near 90Â°F are forecast Jun 10â12, expect reduced output.[DONE]</t>
+          <t>All three CPS SCA60KTL inverters are online and producing as of Jun 9 at 7:38 PM EDT, with the production meter and weather station reporting normally.
+Today's peak hourly output was modest (~130 kW combined around midday) under variable rain conditions, consistent with the Light rain currently at the site.
+The site has been underperforming throughout the 30-day window. The Energy Performance Index averages roughly 0.41, with inverter availability at 100% and 30-day production of 29,929 kWh vs. 35,102 kWh estimate (85%).
+Sampled inverter PV model losses show large DC/AC age losses (~83-88%) and 58% residual loss on Inverter-1, with similar residual losses across all three inverters per the rule tool. This persistent underperformance pattern warrants review.
+Meter-to-inverter ratio is 1.00 (normal). The Performance Index alert from May 24 reflects this ongoing underperformance.
+Forecast calls for light rain and warming highs into the low 90s through Jun 12, limiting production.[DONE]</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="92" customHeight="1">
+          <t>2026-06-10 00:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="106" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>S51958</t>
@@ -670,16 +670,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>All three inverters online and producing as of Jun 9 at 10:08 AM EDT under clear skies (75Â°F). Hardware is communicating normally.
-Site is healthy. The 30-day Energy Performance Index averages 0.94, with inverter availability at 100%.
-Actual vs. expected production tracked at 96% over the last 7 days, and all three inverters are producing in proportion to their ratings. Sampled-inverter PV model losses show only minor age and soiling effects.
-Meter-to-inverter ratio is 1.00, normal. Rule tool flags two configuration items on the Microhard Modem (default alerts not set) â monitoring setup only, no production impact.
-Light rain and highs near 90Â°F are forecast Jun 10â12, which will likely reduce production modestly.[DONE]</t>
+          <t>All three inverters are online and producing as of Jun 9 at 6:00 PM EDT, with the production meter at 769.8 kWh today under light rain.
+Hardware is communicating normally. Current conditions (72Â°F, light rain) are consistent with the reduced afternoon output seen today.
+No production events occurred in the reporting window.
+The 30-day Energy Performance Index averaged 0.95 and inverter availability was 100%. Sampled-inverter PV model losses show routine AC/DC age (~3% each) and minor soiling (~1%); no major losses identified.
+Meter-to-inverter ratio is 1.00, which is normal. The rule tool flagged default-alert configuration items on the Microhard Modem â monitoring-only, no production impact.
+Forecast calls for light rain and highs of 82â91Â°F through Jun 12; expect continued weather-driven variability with no equipment risk.[DONE]</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
+          <t>2026-06-10 00:05 UTC</t>
         </is>
       </c>
     </row>
@@ -696,16 +697,15 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 9 at 11:14 AM EDT, with both inverters reporting through 11:04 AM. Current conditions are clear and 75Â°F, and midday production is tracking actual vs. expected output normally.
-No production events occurred in the reporting period.
-The 30-day Energy Performance Index averaged 0.83, with inverter availability at 100%. Site totals reached 89% of estimated energy. The sampled inverter PV model losses show a residual loss of â26%, indicating actual production is exceeding the model.
-The meter-to-inverter ratio is 1.00, normal. The rule tool flags a high energy ratio (1.21 and 1.30) on both inverters and a production meter capacity mismatch, suggesting PV model or capacity configuration needs review. No active alerts.
-Light rain is forecast Jun 10â12 with highs to 91Â°F, which may modestly reduce production.[DONE]</t>
+          <t>Both inverters are online and producing as of Jun 9 at 7:07 PM EDT, with the site generating 590 kWh today under light rain and overcast conditions. Today's peak hourly output reached ~97 kW around 2:00 PM, consistent with the cloudy weather.
+Over the last 30 days, the Energy Performance Index averaged 0.84 and inverter availability held at 100%. Production totaled 18.4 MWh, or 90% of the estimate. PV model losses for the sampled inverter show ~4% soiling and a large negative residual, suggesting the PV model may be over-predicting.
+The meter-to-inverter ratio is 1.00, normal. An informational EPI alert (index 1.32) triggered Jun 9 at 3:21 PM flags a possible weather station calibration issue, consistent with the negative residual losses.
+Light rain is forecast through Jun 12 with highs reaching 91Â°F, expect continued weather-driven variability.[DONE]</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
+          <t>2026-06-10 00:05 UTC</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,20 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>All five inverters are online and producing as of Jun 9 at 10:36 AM EDT under clear skies (75Â°F). Current hourly output through 10 AM is tracking reduced irradiance this morning, consistent with variable cloud cover earlier in the day.
-Over the last 30 days, the Energy Performance Index averaged about 0.77, with inverter availability at 100%. Sampled Inverter-1 PV model losses show residual loss of 7% plus soiling 3%, suggesting a site-wide cleaning may be worth evaluating.
-The rule tool flags Inverters 2 and 3 with low energy ratios (0.69 and 0.65) and elevated residual losses (29% and 33%) versus peers â consistent underperformance visible in the hourly production chart. Meter-to-inverter ratio is 0.99 (normal). A low-priority Performance Index alert from Jun 8 reflects this ongoing pattern.
-Forecast calls for rain Jun 10â12 with highs near 90Â°F; expect reduced production those days.[DONE]</t>
+          <t>All 5 CPS SCA60KTL inverters online and producing as of Jun 9 at 6:00 PM EDT under light rain. Today's peak hourly output was ~215 kW around 2:00 PM, consistent with overcast conditions.
+30-day Energy Performance Index averages 0.78 with inverter availability at 100%. Production totals 44.5 MWh vs. 56.9 MWh estimated (78%), reflecting frequent rain in the period rather than a discrete event.
+Inverters 2 and 3 consistently produce ~30â35% less than Inverter 1 across every daylight hour, flagged by the rule tool as low energy ratios (0.67 and 0.62) with excessive residual loss. This is a persistent performance issue worth field investigation (string-level checks, combiner/fuses).
+Meter-to-inverter ratio is 0.99 (normal). Sampled Inverter 1 model losses show ~10% soiling loss as the main contributor.
+Forecast is light rain with highs 82â91Â°F through Jun 12; expect continued subdued production.[DONE]</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="99" customHeight="1">
+          <t>2026-06-10 00:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="104" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>S54553</t>
@@ -747,19 +748,21 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>All hardware is communicating normally as of Jun 9 at 8:25 AM PDT, and the SMA SC4000 inverter is producing in line with expected output for the prevailing light rain conditions. No active production events.
-Over the last 30 days, the site has performed well with an average EPI near 1.00 and 100% inverter availability. Total production of 1,081 MWh exceeded estimate by 16%. Sampled-inverter PV model losses and tracker losses show nothing notable.
-Meter-to-inverter ratio is 0.99, normal. The rule tool flagged a configuration item: default alerts (device communication, SEL 351 Breaker Bit) are not enabled on the SEL-351 Relay â a monitoring visibility gap only.
-Forecast shows light rain Jun 10, then clearing to 75â79Â°F Jun 11â12, favorable for strong production midweek.[DONE]</t>
+          <t>All hardware is communicating as of Jun 9 around 5:05 PM PDT, and SMA SC4000 Inverter-1 is producing normally, reaching ~3.4 MW midday under light rain conditions.
+Site is operating normally with no active production events.
+30-day Energy Performance Index averages 1.01 and inverter availability is 100%. 30-day production is 1080 MWh, ~116% of estimate.
+Sampled-inverter PV model losses show typical DC/AC age (~3%) and soiling (~1%); no major losses identified. Tracker losses are negligible (&lt;4 kWh/day).
+Meter-to-inverter ratio is 0.99, normal. The rule tool flagged a high energy ratio (~1.21) and SEL-351 Relay default alerts not enabled â review sensor calibration and relay alert configuration.
+Forecast calls for light rain Jun 10, then clear skies Jun 11â12 with highs of 75â79Â°F, favorable for production.[DONE]</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="98" customHeight="1">
+          <t>2026-06-10 00:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="106" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>S54613</t>
@@ -772,20 +775,20 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>All 32 inverters online and producing as of Jun 9 at 11:26 AM EDT under light rain, consistent with low morning irradiance. No active production event.
-Over the past 30 days, the Energy Performance Index averaged about 0.88, with weather-driven dips on May 23 (0.66), May 26 (0.67), and Jun 1 (0.77).
-Inverter availability averaged 97%, with the lowest day at 76% on May 23. Sampled-inverter PV model losses show modest soiling, downtime, and residual losses â nothing notable.
-Meter-to-inverter ratio is 0.99, normal. The rule tool flagged minor inverter uptime gaps (most at ~98%); no current production correlation.
-Forecast: clear Jun 10 (high 90Â°F), then rain Jun 11â12 with highs near 95Â°F â expect reduced output on the rainy days and possible mild thermal derate.[DONE]</t>
+          <t>All 32 Sungrow SG125 inverters are online and communicating as of Jun 9 at 8:06 PM EDT, with all balance-of-plant devices reporting normally. Today's production was limited by cloud cover; recent clear days (Jun 3â5) reached the 4 MW AC cap during midday hours per the production and expected chart.
+No discrete production events in the last two weeks. Day-to-day variability on May 22â26 and Jun 1â2 aligns with weather, not equipment issues.
+30-day Energy Performance Index averaged 0.88 and inverter availability 97%. Sampled-inverter PV model losses show ~8% residual and ~7% combined age-related losses; no major event-driven losses.
+Meter-to-inverter ratio 0.99, normal. Rule tool clean; no active alerts.
+Forecast calls for light rain and highs to 99Â°F Jun 10â12; expect reduced output and possible high-temperature derating.[DONE]</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="114" customHeight="1">
+          <t>2026-06-10 00:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>S54681</t>
@@ -798,20 +801,20 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Site gateway PowerLogger 1000 and Cell Modem (RV50) stopped reporting on Jun 6 at 3:05 PM EDT, halting all telemetry uploads since. However, inverter production through Jun 6 shows normal output, and the meter-to-inverter ratio of 0.99 over 30 days confirms metering integrity through that date. Current production state after Jun 6 cannot be verified until the data logger is restored.
-No production events identified in the reporting window. Inverter 8 consistently produces ~75 kW vs. ~125 kW peers â a persistent performance issue, not a discrete event.
-30-day EPI averages 0.97; inverter availability 99%. No major losses on the sampled inverter.
-Active alerts include External Fan Errors on Inverters 5 and 8 (Jun 6) and weather station irradiance/temperature invalid flags affecting expected energy inputs.
-Light rain forecast through Jun 12 with mild temperatures; reduced production expected.[DONE]</t>
+          <t>All 24 CPS SCH125kTL inverters are online and producing in line with peers as of Jun 9 at 8:06 PM EDT, with current output tapering normally near sunset under light rain.
+Inv-8 shows a persistent ~25% deficit vs. peers (capped near 75 kW during midday hours) visible across recent days in the production chart, coincident with an active External Fan Err fault triggered Jun 9 at 3:42 PM. Classify as partial capability on ~125 kW (~3% of site); ongoing impact ~150 kWh/day.
+30-day EPI averages 0.97 with availability at 99%. No major losses identified on the sampled inverter.
+Meter-to-inverter ratio is 0.99 â normal. Rule tool reports stale comm/weather flags from earlier in the day; hardware table shows all devices uploading within minutes â disregard as stale.
+Forecast: rain and light rain through Jun 12, highs 79â82Â°F. Expect reduced but normal production.[DONE]</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="113" customHeight="1">
+          <t>2026-06-10 00:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="118" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>S59656</t>
@@ -824,20 +827,19 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>All 80 SunGrow SG125HV inverters are communicating and producing as of Jun 9 at 11:26 AM EDT, with site output ramping under clear skies (84Â°F, light wind).
-The site is operating normally. Three active alerts are advisory: a stale tracker-comm alert on the original GameChange Tracker Control (Aug 29, 2025), a tracker E-Stop on Tracker Control 2.1 triggered Jun 9 at 9:56 AM, and a Rule Tool summary. Tracker lost energy reads 0 kWh across the last 7 days.
-30-day EPI averages 0.94 with inverter availability at 99%. No major losses identified on the sampled inverter.
-Meter-to-inverter ratio is 0.99 (normal). Rule Tool flags soiling on inverters 22, 39, and 42 (5â6%), a POA sensor configured as fixed-tilt rather than tracking, and tracker configuration gaps worth review.
-Forecast: light rain Jun 10â11, rain Jun 12, highs to 99Â°F â expect reduced output and possible heat derating.[DONE]</t>
+          <t>All 80 SunGrow inverters online and reporting as of Jun 9 at 8:06 PM EDT, with the site producing normally through the day under light rain. Current weather is 77Â°F with light rain; peak hourly output reached ~9.4 MW around midday per the production and expected chart.
+30-day EPI averages 0.94 and inverter availability 99%. Production-to-estimate ratio is 91%. Sampled-inverter PV model losses show no major losses; tracker lost energy is 0 kWh over 7 days.
+Meter-to-inverter ratio is 0.99 (normal). Active alerts: a Tracker Control 2.1 E-Stop/Tracking Disabled fault (Jun 9, 7:04 PM) â no tracker energy loss observed; an Aug 2025 comm-loss alert on the original GameChange Tracker Control remains stale. Rule tool flags ~5â6% soiling on inverters 22, 39, 42, and a POA sensor tilt/azimuth misconfiguration worth review.
+Forecast: light rain with highs 93â99Â°F through Jun 12; expect moderate weather-driven production variability.[DONE]</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="94" customHeight="1">
+          <t>2026-06-10 00:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="99" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>S63837</t>
@@ -850,19 +852,20 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>All 24 inverters online and producing as of Jun 9 at 11:27 AM EDT, with clear skies and 84Â°F. Site is operating normally; current-day production is ramping through the morning per the production and expected chart.
-30-day Energy Performance Index averages 0.99 with inverter availability at 100%. Sampled-inverter PV model losses show no notable issues; tracker losses average ~70 kWh/day, minimal.
-Meter-to-inverter ratio is 0.98, normal. Rule tool flags three trackers stuck at fixed angles (A1 S 22, S 54, S 79) and elevated error on A1 S 46 â worth field review but low energy impact. AE Smart UPS default alerts not set.
-Forecast: clear Jun 10â11 with highs 93Â°F, light rain Jun 12 (97Â°F). Favorable production conditions through midweek.[DONE]</t>
+          <t>All 24 inverters online and reporting as of Jun 9 at 8:07 PM EDT, with the site producing 24,000 kWh today against a 24,475 kWh estimate.
+Current conditions are clear and 82Â°F at sunset, so production is finished for the day.
+30-day Energy Performance Index averages 0.99 with inverter availability at 100% over the last 10 days. PV model losses on the sampled inverter show no major issues; tracker lost energy averages ~76 kWh/day, minor.
+Meter-to-inverter ratio is 0.98, normal. The rule tool flagged three trackers stuck at fixed angles (Position A1 S 22, S 54, S 79) and an average error of 6.2Â° on S 46 â worth field verification but low energy impact.
+Forecast is clear to light rain with highs reaching 97Â°F by Jun 12; monitor for possible high-temperature derating midweek.[DONE]</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="86" customHeight="1">
+          <t>2026-06-10 00:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="100" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>S63838</t>
@@ -875,20 +878,19 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>All 28 inverters and supporting hardware are communicating normally as of Jun 9 at 11:27 AM EDT, with the site producing under clear skies (84Â°F). Morning ramp is tracking expected output closely.
-30-day Energy Performance Index averages 0.97 with inverter availability at 100%. Estimated energy ratio is 87%.
-Sampled-inverter PV model losses show only routine age and soiling. Tracker losses are minor (~10â40 kWh/day).
-Meter-to-inverter ratio is 0.98, normal. Rule tool flags Position A1 S 16 stuck at 0Â° and AE Smart UPS default alerts unset â monitoring items only.
-Forecast is clear Jun 10â11 with highs near 93Â°F, then light rain Jun 12; no expected operational impact.[DONE]</t>
+          <t>All 28 inverters online and reporting fresh telemetry as of Jun 9 at 8:07 PM EDT, with the site past sunset under clear 82Â°F skies. Earlier today the site reached ~3.0 MW around noon, consistent with AC capacity, though afternoon production was variable with passing clouds.
+Over the last 30 days, the site averaged an EPI of 0.98 and 99.9% inverter availability. Sampled-inverter PV model losses show only minor age and soiling losses; no major losses identified.
+Meter-to-inverter ratio is 0.98, normal. The rule tool flags Tracker "Position A1 S 16" stuck at 0Â° and AE Smart UPS default alerts not set â monitoring items only. Tracker losses remain small (~24 kWh on Jun 9).
+Forecast: clear Jun 10, light rain Jun 11, clear Jun 12 with highs reaching 97Â°F â monitor for heat derating.[DONE]</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="117" customHeight="1">
+          <t>2026-06-10 00:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="92" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>S63839</t>
@@ -901,20 +903,19 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>All 24 inverters online and producing as of Jun 9 at 11:27 AM EDT, with light rain and reduced irradiance limiting current output. Site weather is mild (86Â°F, 3 mph wind).
-Recent daily production has tracked expected output closely (101% actual/expected over 7 days), confirming normal operations.
-30-day Energy Performance Index averages 0.99 and inverter availability is 100%. Sampled-inverter PV model losses show no notable issues; tracker losses are minor (~20â55 kWh/day).
-Meter-to-inverter ratio is 0.98 â normal. The rule tool flagged 0% availability on the "10 String" and "11 String" inverter groups, but production data confirms these groups are generating normally â a configuration artifact only. NCU 1 reports two trackers stuck at fixed angles (Position A1 S 10 and S 56); worth field verification.
-Forecast: clear and warm Jun 10â11 (highs 93â97Â°F), favorable for production; light rain returns Jun 12.[DONE]</t>
+          <t>All 24 inverters online and producing as of Jun 9 at 8:07 PM EDT, with clear skies and 82Â°F. Current-day production is tracking expected output closely, with a peak around 2.6 MW midday.
+30-day Energy Performance Index averages 0.99 and inverter availability is 100% over the last 9 days (site 30-day 99.7%). Sampled-inverter PV model losses show no notable findings; tracker losses are minor (~30â55 kWh/day).
+Meter-to-inverter ratio is 0.98, normal. The rule tool flags two NCU 1 trackers stuck (Position A1 S 10 at 22.9Â°, A1 S 56 at -21.3Â°) and inverter-group configuration items; impact is limited based on tracker losses.
+Forecast: clear Jun 10, light rain Jun 11â12 with highs to 99Â°F â some heat derating possible.[DONE]</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="114" customHeight="1">
+          <t>2026-06-10 00:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="108" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>S63840</t>
@@ -927,20 +928,19 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>All 24 inverters online and reporting as of Jun 9 at 11:27 AM EDT, with light rain (73Â°F) limiting current output. Morning production is tracking expected under overcast conditions per the hourly production and expected chart.
-No production events in the last two weeks. Daily output has varied with weather, with strong days Jun 3â5 (~32 MWh) and weather-limited days Jun 7â8.
-30-day Energy Performance Index averages 0.96 with inverter availability at 100%. Sampled-inverter PV model losses and tracker losses show nothing notable.
-Meter-to-inverter ratio is 1.02, slightly elevated. The rule tool flags a meter phase current/PF imbalance, a POA insolation mismatch of +61% on PY0 (check azimuth/tilt), and low BPOA insolation â review sensor calibration as these affect EPI integrity.
-Forecast: clear Jun 10 (90Â°F) then light rain Jun 11â12; expect strong production Tuesday, reduced midweek.[DONE]</t>
+          <t>All 24 inverters online and reporting as of Jun 9 at 8:07 PM EDT, with the site in post-sunset hours. Recent days have shown variable production consistent with mixed insolation; Jun 8 and Jun 9 ran well below clear-sky days earlier in the week per the production and expected chart.
+30-day Energy Performance Index averages 0.96 with inverter availability at 100%. Sampled-inverter PV model losses show no notable items; tracker losses are under 1 kWh/day.
+Meter-to-inverter ratio is 0.98 over 30 days â normal. The rule tool flags a POA insolation mismatch (+61% vs other sensors) on the Kipp &amp; Zonen SMP-12 POA pyranometer and low BPOA insolation â review sensor calibration/tilt as this can bias EPI. AE Smart UPS default alerts unset; meter PF near zero noted.
+Forecast is clear with highs 88â93Â°F through Jun 12 â favorable production conditions.[DONE]</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="105" customHeight="1">
+          <t>2026-06-10 00:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>S64602</t>
@@ -953,20 +953,19 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>All 40 inverters communicating as of Jun 9 at 11:27 AM EDT, with the site producing under light rain. Today's production ramped to ~3.8 MW by 10 AM, consistent with overcast conditions.
-30-day Energy Performance Index averages 0.92 with inverter availability at 100%. Sampled inverter shows minor soiling (~1%) and age losses; no major losses identified.
-Meter-to-inverter ratio is 0.98, normal. The BPOA pyranometer (PY2) has been offline since Jun 16, 2025; backup POA sensor remains operational.
-Tracker control (ST0) reports multiple slave positions stuck at 0Â° and ~26Â° average tracker error on three rows, with tracker losses running ~120 kWh/day (&lt;0.3% of site output).
-Forecast calls for light rain and highs of 93â99Â°F through Jun 12; expect continued reduced output with possible thermal derating on the warmer days.[DONE]</t>
+          <t>All 40 inverters communicating as of Jun 9 at 8:07 PM EDT, with the most recent uploads within minutes. Site is producing under light rain after a cloudy afternoon; peak output today reached ~4.7 MW around 11 AM.
+30-day Energy Performance Index averages 0.93 with no major drops, and inverter availability is 100% in the past week (site 30-day: 99.83%). No notable PV model losses on the sampled inverter; tracker lost energy runs ~50â125 kWh/day, a minor performance drag tied to several stuck/erroring tracker rows.
+Meter-to-inverter ratio is 0.98, normal. Monitoring flags: PYRANOMETER - BPOA (PY2) offline since Jun 16, 2025 (equipment repair needed); Solar FlexRack tracker slave SOC alarms (S63, S81) since Apr 30; multiple tracker positions reading 0Â° with ~26Â° average error on S10/S63/S81 per the rule tool.
+Forecast: light rain with highs climbing to 100Â°F by Jun 12 â expect humid, partly clouded production and monitor for heat derating.[DONE]</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="98" customHeight="1">
+          <t>2026-06-10 00:08 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="114" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>S64603</t>
@@ -979,20 +978,20 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>All 72 inverters are communicating and operating as of Jun 9 at 11:28 AM EDT under light rain with reduced irradiance. Today's production has ramped through the morning consistent with the overcast conditions.
-A brief mid-morning dip on Jun 5 (EPI 0.81) shows in the PV model losses for the sampled inverter as ~210 kWh of downtime, but daily availability and meter totals remained healthy.
-30-day EPI averages 0.96 with inverter availability at 99%. Sampled soiling loss ~5% is the main detractor.
-Meter-to-inverter ratio is 0.98 (normal). Open tracker alerts on ST1 (not responding since 10:18 AM, low SoC, e-stop) and ST2 (low SoC) should be reviewed; tracker losses remain under 200 kWh/day.
-Forecast is light rain with highs 93â100Â°F through Jun 12; no derating expected.[DONE]</t>
+          <t>All 72 inverters communicating as of Jun 9 at 8:08 PM EDT, with production tapering normally into evening under light rain. Conditions are intermittently cloudy, consistent with reduced midday output today.
+No production events in the reporting window. A brief site dip on Jun 5 (EPI 0.81, availability 88%) recovered the same day.
+30-day EPI averages 0.97 with inverter availability at 99%. Sampled-inverter losses and tracker losses are minor.
+Meter-to-inverter ratio is 0.98 (normal). Open tracker alerts on ST1 (e-stop, comm loss since Jun 9 at 10:18 AM) and ST2 (low SoC), plus a rule tool flag noting several trackers with elevated position error or stuck at 0Â°. A production meter current mismatch alert (A/B/C phases) triggered Jun 9 at 7:44 PM â worth monitoring for CT/wiring issues.
+Forecast is light rain with highs 95â100Â°F through Jun 12; expect variable output and possible heat derating.[DONE]</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="109" customHeight="1">
+          <t>2026-06-10 00:08 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="102" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>S65216</t>
@@ -1005,16 +1004,16 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 9 at 8:28 AM PDT, with Inverter 1 producing 2,625 kWh in the 7:00 AM hour. Conditions are clear and cool, supporting normal operations.
-Production was reduced on Jun 8 (10.7 MWh vs. ~28 MWh estimated) and Jun 3 (17.4 MWh), consistent with low irradiance on those days per the PV model. May 28â29 also showed depressed output (~9.8â16.9 MWh) with one availability dip to 85% on May 28; no current impact.
-30-day EPI averages ~0.99 and inverter availability is 99%. Site reached 99% of estimate over 30 days. Sampled-inverter losses and tracker losses (3â28 kWh/day) are minor.
-Meter-to-inverter ratio is 0.99, normal. Rule tool flagged high energy ratio on Jun 8 from low expected output â a mathematical artifact, not a performance issue.
-Forecast is clear with highs rising to 82Â°F by Jun 12, favorable for production.[DONE]</t>
+          <t>Inverter 1 is online and producing, last reporting at 5:05 PM PDT on Jun 9, with all other hardware communicating normally. Current output is tracking expected energy closely under clear skies and 57Â°F.
+No production events occurred in the reporting period. Variable output on Jun 3, Jun 5, and Jun 8 reflects intermittent cloud cover, not equipment issues.
+30-day Energy Performance Index averaged 0.99 with inverter availability at 99%. Production reached 99% of estimate. No major losses identified in the sampled inverter PV model losses or tracker losses.
+Meter-to-inverter ratio is 0.99, normal. The rule tool high energy ratio flags reflect partial-day data and are not actionable.
+Forecast is clear with highs rising to 82Â°F by Jun 12 â favorable production conditions with no derating concerns.[DONE]</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
+          <t>2026-06-10 00:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1031,20 +1030,21 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>All 40 inverters are communicating as of Jun 9 at 11:28 AM EDT, with the site producing through light rain this morning. Today's output is weather-limited (~4.5 MWh by 11 AM), consistent with overcast conditions.
-30-day inverter availability is 100%, and production reached 94% of estimate (1,262 MWh actual vs 1,328 MWh estimated).
-The Energy Performance Index averages 1.17, persistently above 1.1, suggesting a PV model or pyranometer calibration issue rather than a performance problem.
-Meter-to-inverter ratio is 0.98 (normal). The rule tool flags stuck AC voltage telemetry on all 40 inverters, several tracker positions stuck at 0Â°, and ~39Â° average tracker error on TCU 96â108 â monitoring/data quality flags with no production correlation (tracker losses &lt;3 kWh/day).
-Forecast calls for rain and highs to 99Â°F through Jun 12; expect reduced output and possible thermal derating.[DONE]</t>
+          <t>All 40 inverters communicating as of Jun 9 at 8:08 PM EDT, with site availability at 100% over the last 30 days.
+Current conditions are light rain at 77Â°F, and today's production reflects a cloudy/rainy profile, peaking near 3.7 MW at 1:00 PM versus ~5 MW expected.
+The INVERTER 6 invalid-data warning that triggered at 8:03 PM is a brief end-of-day comm blip; Last Update is current.
+The 30-day Energy Performance Index averages ~1.16, consistently above 1.1, suggesting a PV model or POA sensor calibration issue worth review. 30-day production is 1,246 MWh (94% of estimate).
+Meter-to-inverter ratio is 0.98 (normal). Rule tool flags stuck VacA/VacB/VacC telemetry across all 40 inverters and many trackers stuck at 0Â° â data-quality flags, not production impacts (tracker losses &lt;3 kWh/day).
+Forecast: light rain through Jun 10, then hot (97Â°F) Jun 11â12 â monitor for thermal derate.[DONE]</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="106" customHeight="1">
+          <t>2026-06-10 00:08 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="99" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>S65785</t>
@@ -1057,19 +1057,19 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>All 24 inverters online and producing normally as of Jun 9 at 11:28 AM EDT, with clear skies and 79Â°F supporting strong morning output near 3 MW AC capacity per the production and expected chart.
-30-day EPI averages 0.96 with inverter availability at 100%. 30-day production totaled 814 MWh, 103% of estimate. Sampled-inverter PV model losses show no major issues; tracker losses are minimal (~7 kWh/day).
-Meter-to-inverter ratio is 0.98, normal. The rule tool flags excessive soiling on INV-3, 8, and 17 (~9â11%) and a tracker position error of 33Â° on TCU 87 â worth monitoring. Active alerts include a UPS battery over-temperature (Jun 9 at 9:14 AM) and the standing tracker TCU 87 blocked-axis warning from Apr 20.
-Forecast calls for light rain Jun 10â12 with highs to 97Â°F; expect reduced output and possible mild thermal derating.[DONE]</t>
+          <t>All 24 inverters online and producing normally as of Jun 9 at 8:08 PM EDT, with the site tracking expected output closely through the afternoon on the production and expected chart. Clear skies, 77Â°F, light winds.
+30-day Energy Performance Index averages 0.96 with inverter availability at 100%. Production totaled 812 MWh vs. 791 MWh estimate (103%). Sampled-inverter PV model losses and tracker losses (~7 kWh/day) are minor.
+Meter-to-inverter ratio is 0.98, normal. The rule tool flags excessive soiling on Inverters 3, 8, and 17 (~9-11%) and a tracker position error of ~33Â° on TCU 87. An ALSOENERGY Smart UPS Battery Over Temperature alert triggered Jun 9 at 9:14 AM; the UPS continues reporting.
+Forecast: light rain and highs 90-97Â°F Jun 10-12, which may modestly reduce output.[DONE]</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="116" customHeight="1">
+          <t>2026-06-10 00:09 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="107" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>S65786</t>
@@ -1082,20 +1082,19 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>All 16 inverters online and producing as of Jun 9 at 11:29 AM EDT under light rain and overcast skies, which is suppressing today's output (morning peak ~793 kW at 10 AM).
-No production events in the reporting period. Recent clear days (Jun 3â5) reached the 2,000 kW AC cap with actual/expected at 96%.
-30-day Energy Performance Index averages 0.91 and inverter availability is 99%. Sampled-inverter PV model shows no major losses; tracker losses are negligible (~5 kWh/day).
-Meter-to-inverter ratio is 0.98 (normal). A UPS Battery Over Temperature warning triggered Jun 9 at 11:18 AM â monitoring infrastructure only, no production impact. Rule tool flags Tracker Position TCU 24 stuck at 0Â° and back-of-module temp below ambient; worth verifying sensor and tracker calibration.
-Forecast: light rain and highs 91â99Â°F through Jun 12; expect continued weather-driven variability with possible heat derating midweek.[DONE]</t>
+          <t>All 16 inverters online and producing as of Jun 9 at 8:08 PM EDT, with the site reaching ~2,000 kW peak hourly output earlier today per the production and expected chart. Light rain and variable cloud cover suppressed midday output today and on Jun 7â8, consistent with weather.
+30-day Energy Performance Index averaged 0.92 and inverter availability averaged 100%. Sampled-inverter PV model losses show no major issues; tracker losses are negligible (~2â5 kWh/day).
+Meter-to-inverter ratio is 0.98, normal. Rule tool flags TCU 24 stuck at 0Â° and a weather station module-temp sensor reading below ambient â review the back-of-module sensor calibration, as it can affect expected energy.
+Forecast calls for light rain and highs near 93â100Â°F through Jun 12; high temperatures may cause minor inverter derating but no stow risk with light winds.[DONE]</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="113" customHeight="1">
+          <t>2026-06-10 00:09 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>S65787</t>
@@ -1108,20 +1107,20 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>All 80 inverters online and producing as of Jun 9 at 11:29 AM EDT, with the site ramping under light rain (88Â°F). Today's production is tracking the expected output curve through mid-morning.
-Recent peak days (Jun 3â5) hit ~112 MWh against the ~88 MWh estimate, confirming healthy plant output.
-30-day EPI averages 0.97 and inverter availability is 99%, with a brief dip to 72% on May 30. Sampled INV 25 shows ~7% soiling loss as the main recoverable loss; tracker losses are minor (~50 kWh/day).
-Meter-to-inverter ratio is 0.98 (normal). A May 17 transformer 90Â°C liquid temp fault (IO2) remains unresolved but shows no production correlation. Rule tool flags several stuck/misaligned trackers (TCU 39, 72, 161, 6, 16) and a POA pyranometer reading ~72% high â worth review for EPI integrity.
-Forecast: clear Jun 10, then light rain and highs near 99Â°F Jun 11â12; watch for thermal derate.[DONE]</t>
+          <t>All 80 inverters are communicating and operating as of Jun 9 at 8:09 PM EDT, with the production meter, weather station, and trackers reporting normally. Light rain is on site at 79Â°F, with reduced afternoon production today consistent with overcast conditions.
+No production events in the last two weeks. Daily output has tracked the site performance estimate closely, with full-capacity hours (~9,996 kW) observed Jun 3â5.
+30-day EPI averages 0.97 and inverter availability is 99%. No major losses identified on the sampled inverter; tracker losses are minor (~24â50 kWh/day).
+Meter-to-inverter ratio is 0.98 (normal). A May 17 transformer 90Â°C liquid-temp fault and several rule tool tracker-error and POA insolation-mismatch flags are open with no production correlation; worth review for sensor and tracker alignment.
+Forecast is light rain with highs 93â99Â°F through Jun 12; expect variable production and some heat-related derate risk.[DONE]</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="98" customHeight="1">
+          <t>2026-06-10 00:09 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="108" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>S65788</t>
@@ -1134,20 +1133,20 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>INVERTER 2.6 has been offline since May 20 at 6:17 PM EDT, confirmed by the meter-to-inverter ratio of 0.98 (normal range, indicating the unit is not producing).
-This is an outage of ~125 kW (~2.5% of site capacity), ~14 MWh lost over ~20 days at ~0.7 MWh/day expected. The remaining 39 inverters are producing normally under clear skies at 82Â°F.
-30-day EPI averages 0.88 and inverter availability 98%, both consistent with the single-inverter outage. Tracker losses are minor (~17 kWh/day).
-Rule Tool flags multiple trackers stuck at 0Â° (TCU 49, 131, 153) and elevated tracker errors on TCUs 1, 4, 78, 151 â worth field verification but low energy impact.
-Forecast: clear Jun 10, then light rain/rain Jun 11â12 with highs near 99Â°F. Heat may cause mild inverter derating.[DONE]</t>
+          <t>All 40 inverters communicating as of Jun 9 at 8:09 PM EDT, with site producing through a light-rain afternoon. Today's peak hourly output reached ~4.9 MW around noon before clouds and rain reduced afternoon output, yielding a partial-day EPI of 0.68. Recent days track expected output closely.
+No production events in the last two weeks. Jun 8 and Jun 9 both saw weather-driven dips consistent with rain, not equipment issues.
+30-day EPI averages 0.88 and inverter availability 97%. Production reached 91% of monthly estimate. Sampled-inverter and tracker losses show nothing notable.
+Meter-to-inverter ratio is 0.98, normal. One Rule Tool informational alert from Jun 1 has no production correlation.
+Forecast is light rain to rain Jun 10â12 with highs reaching 100Â°F by Jun 12; expect weather-limited output and possible temperature derating mid-week.[DONE]</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="141" customHeight="1">
+          <t>2026-06-10 00:09 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="130" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>S65918</t>
@@ -1160,20 +1159,20 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Site is producing but with multiple equipment issues. As of Jun 9 at 11:30 AM EDT, 33 of 35 inverters are reporting current production. INV-7 (last upload Jun 2) and INV-9 (last upload Jun 2) show meter-to-inverter ratio near 1.00 today, consistent with confirmed outages rather than comm loss. INV-17, INV-23, INV-35, INV-13, INV-34 have been offline 7-63 days â sustained production loss.
-Approximately 7 inverters (~20% of capacity) currently offline. Estimated loss ~12 MWh/week (~250 kW affected, ~7 hrs/day production). New urgent faults today on INV-1 (External Fan Damaged), INV-4, INV-14 (Hardware self test failure) require attention via active alerts.
-30-day site production totals 721 MWh vs 1,782 MWh estimate (40%), reflecting widespread inverter unavailability and overcast periods.
-METER - PRODUCTION 1 not responding since May 13; meter-to-inverter ratio currently elevated at 1.08. Weather station and pyranometers offline since May 13 â POA/GHI/BPOA invalid, affecting EPI calculation. Tracker Control 1 and 2 reporting average ~37Â° position errors.
-Light rain today through Jun 12; clear Jun 11.[DONE]</t>
+          <t>Site producing through evening with light rain; meter shows 22,830 kWh today across METER 2 and METER 3.
+Several inverters are confirmed offline based on hourly production: INV-4 (since Jun 9 ~1 PM EDT, forced outage â Shutdown Command), INV-7 and INV-9 (since Jun 2, forced outages), INV-13 (since May 21), INV-17 (since Apr 22), INV-22 (Jun 9 ~5 PM, arc fault), INV-23 (since Apr 10), INV-35 (since Apr 6). INV-14 tripped Jun 9 7:21 AM (hardware self-test) but resumed. Combined ~1.4 MW offline; today's loss ~6â8 MWh vs. ~61 MWh daily estimate.
+30-day production totals 740 MWh vs. ~1,782 MWh estimate (42%), reflecting cumulative inverter outages and rainy periods; EPI and availability are uncomputable due to weather station data issues.
+METER 1 not reporting since Apr 27; meter-to-inverter ratio on reporting meters ~0.79 â low, likely metering data gap. Multiple active fault and comm alerts outstanding, plus pyranometer/weather station offline.
+Forecast: rain and heavy rain Jun 10â12, reduced production expected.[DONE]</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="116" customHeight="1">
+          <t>2026-06-10 00:10 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="103" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>S66000</t>
@@ -1186,20 +1185,20 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Inverter 1 is online and producing, with the datalogger and meter reporting fresh telemetry as of 8:30 AM PDT. Current conditions are light rain at 52Â°F, consistent with the subdued morning ramp seen in the production and expected chart.
-No production events identified in the last 2 weeks. June 8 was a low-output day (~5.8 MWh) consistent with overcast conditions, with actual tracking expected.
-The 30-day Energy Performance Index averages 1.09, slightly elevated and worth monitoring for possible PV model or POA sensor calibration drift. Inverter availability is 100%. Tracker losses are negligible (&lt;13 kWh/day).
-Meter-to-inverter ratio is 0.99, normal. The rule tool flags the POA pyranometer as configured fixed-tilt on a tracker site â recommend reviewing sensor configuration as this may explain the elevated EPI.
-Forecast clears to 75â77Â°F Jun 11â12, supporting strong production after light rain Jun 10.[DONE]</t>
+          <t>All hardware is communicating as of Jun 9 at 5:09 PM PDT, with Inverter 1 producing normally through the afternoon under light rain conditions. Today's production tracks expected output closely, peaking near 2.0 MW.
+Over the last 30 days, the site is performing well: EPI averages 1.09 and inverter availability is 100%. Total production of 553 MWh is 123% of estimate.
+The persistently elevated EPI (&gt;1.1 on several days) suggests a possible PV model or pyranometer calibration drift worth reviewing. Tracker losses are negligible (&lt;13 kWh/day).
+Meter-to-inverter ratio is 1.01, slightly elevated but consistent over the period â worth monitoring CT/meter configuration. No active alerts and rule tool is clean.
+Forecast: light rain Jun 10, then clear and warm (75â77Â°F) Jun 11â12, supporting strong production.[DONE]</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="99" customHeight="1">
+          <t>2026-06-10 00:10 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="93" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>S66001</t>
@@ -1212,20 +1211,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Inverter 1 is online and producing, with the hardware fleet reporting fresh telemetry as of Jun 9 at 8:30 AM PDT. Morning output is tracking expected under light rain (486 kWh at 7:00 AM vs. 418 kWh expected per the production and expected chart).
-Jun 8 was a heavy overcast day (6,655 kWh on the meter), consistent with weather rather than an equipment issue.
-30-day EPI averages 1.02 and inverter availability is 100%. Production totaled 832 MWh against a 728 MWh estimate (114%). No notable losses on the PV model chart; tracker losses are minimal.
-Meter-to-inverter ratio is 0.99, normal. The rule tool flagged a weather station high-temperature data check; no production impact.
-Light rain today, then clearing Jun 11â12 with highs in the upper 70s â favorable for production.[DONE]</t>
+          <t>Inverter 1 is online and producing, with hardware last update at Jun 9 at 5:09 PM PDT. Current conditions are light rain at 59Â°F, and today's production reached ~2.5 MW at midday under variable irradiance.
+30-day Energy Performance Index averages 1.02 and inverter availability is 100%. Total production of 829 MWh is 114% of estimate. No major losses identified on the sampled inverter; tracker losses are minimal (&lt;25 kWh/day).
+Meter-to-inverter ratio is 0.99 (normal). The rule tool flagged a high energy ratio (1.12) and elevated weather station temperature â worth monitoring for sensor calibration but no production impact.
+Forecast: light rain Jun 10, clearing Jun 11â12 with highs to 79Â°F. Favorable production conditions ahead.[DONE]</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="130" customHeight="1">
+          <t>2026-06-10 00:10 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="121" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>S66930</t>
@@ -1238,20 +1236,21 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Elk Solar is operating at partial capability as of Jun 9 at 11:30 AM EDT. The production meter has been offline for the full 30-day window (no meter data), so inverter telemetry is authoritative.
-Inverters 01.02 and 01.15 have been offline since May 27, and inverters 01.08â01.14 dropped offline on Jun 8 â collectively ~9 inverters (~21% of site capacity) in an outage. Estimated loss ~17 MWh (Block 1 inverters offline, ~750 kWh/day per sampled inverter, 01.02 down ~13 days plus seven units down ~2 days). Weather is light rain, limiting today's irradiance.
-30-day EPI is unavailable (meter down); inverter production totals 967 MWh vs. 1,308 MWh estimate (74%). Inverter availability averaged 95%, dropping to 77% on Jun 8.
-Monitoring flags: production meter offline (meter-to-inverter ratio not computable), multiple tracker motor current and position anomalies on NCU 1/NCU 2, weather station POA +19% vs. peers, and inverter 01.15 telemetry stuck at zero.
-Forecast: clear Jun 10, then rain Jun 11â12 with highs to 99Â°F.[DONE]</t>
+          <t>Inverter 01.02 has been offline since May 27 at 3:29 AM EDT (forced outage, ~750 kWh/day downtime loss on sampled inverter). Inverter 01.15 also shows zero production with stuck AC telemetry â concurrent outage.
+Inverters 01.08â01.14 show reduced availability ~30% with ~575â633 kWh/day downtime loss each. Combined ~9 inverter outage represents ~1.1 MW affected capacity, ~5.6 MWh/day loss, ~78 MWh over 14 days.
+Today's site peak was ~4.3 MW around noon under light rain; weather-limited.
+30-day inverter availability 95%; actual/expected 90%. Inverters 01.01 and 01.05 show low energy ratios (0.34, 0.50) â investigate.
+Production meter reports zero (meter/inverter ratio undefined); voltage calc 173% of meter power â CT/metering issue. NCU 1 and NCU 2 show stuck trackers and abnormal motor currents; tracker losses ~44â73 kWh/day.
+Forecast: rain through Jun 12, highs 93â100Â°F â expect weather-limited output and possible thermal derating.[DONE]</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="120" customHeight="1">
+          <t>2026-06-10 00:10 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="99" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>S68112</t>
@@ -1264,20 +1263,20 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 9 at 8:30 AM PDT, with Inverter 1 producing 1,317 kWh in the 7 AM hour under light rain. Current conditions are overcast with light rain, consistent with the reduced output seen on Jun 8 and the morning of Jun 9.
-No production events identified in the last two weeks. Day-to-day variability on the production chart tracks weather, not equipment issues.
-30-day inverter availability is 100%. The 30-day average Energy Performance Index is 1.06, persistently above 1.0, suggesting a PV model or pyranometer calibration issue rather than a performance problem.
-Meter-to-inverter ratio is 0.99, normal. The rule tool flags high energy ratio on the meter and inverter, BPOA insolation low, and POA insolation +55% above other sensors â recommend reviewing POA tilt/azimuth configuration and BPOA sensor.
-Forecast: light rain Jun 10, then clear skies and warming highs (75â79Â°F) Jun 11â12, favorable for production.[DONE]</t>
+          <t>Inverter 1 is online and producing, with the hardware last reporting at 5:07 PM PDT on Jun 9. Light rain is reducing output today, with a peak hourly output of ~2.4 MWh this morning per the production chart.
+No production events in the last 30 days. Inverter availability held at 100%.
+The 30-day EPI averaged 1.07, persistently above 1.0, suggesting a PV model or POA calibration issue rather than a plant problem. Tracker losses were minimal (~0.9â59 kWh/day).
+Meter-to-inverter ratio is 0.99, normal. The rule tool flags POA insolation +55% higher than other sensors and low BPOA â consistent with the elevated EPI and warrants a pyranometer azimuth/tilt and calibration check.
+Forecast: light rain Jun 10, then clear and warm Jun 11â12 (75â79Â°F), favorable for production.[DONE]</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="104" customHeight="1">
+          <t>2026-06-10 00:10 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="82" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>S68113</t>
@@ -1290,20 +1289,19 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>All hardware is communicating as of Jun 9 at 8:29 AM PDT, with Inverter 1 producing in line with expected output through the morning under light rain.
-Recent daily production has been variable due to cloud cover, with low output on Jun 8 (8.8 MWh) and Jun 5 (16.3 MWh), but actual vs. expected tracking remains close, indicating normal weather-driven variation rather than a performance issue.
-30-day Energy Performance Index averages 0.99 and inverter availability is 100%. Total production of 758 MWh exceeds the 710 MWh estimate (107%). No major sampled-inverter or tracker losses identified.
-Meter-to-inverter ratio is 0.99, normal. No active alerts and the rule tool reports all tests passing.
-Forecast shows light rain Jun 10 followed by clear, warm conditions Jun 11â12 (highs 75â77Â°F), favorable for production.[DONE]</t>
+          <t>Marble Solar is operating normally as of Jun 9 at 5:09 PM PDT. All hardware is communicating, and Inverter 1 produced about 2.6 MW peak earlier today under clear skies and 61Â°F temperatures.
+30-day Energy Performance Index averages 0.99 with inverter availability at 100%. Total production of 758 MWh is 107% of estimate. No major losses identified in the PV model for the sampled inverter; tracker losses are minimal (under 26 kWh/day).
+Meter-to-inverter ratio is 0.99, within normal range. No active alerts or monitoring flags.
+Forecast shows light rain Jun 10, then clear and warm (75â77Â°F) Jun 11â12 â favorable production conditions ahead.[DONE]</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="119" customHeight="1">
+          <t>2026-06-10 00:10 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="125" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>S70532</t>
@@ -1316,21 +1314,21 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>All 40 inverters are online and producing, with light rain limiting current output to ~1.8 MW around 10 AM EDT. Tracker Controller 1 has been offline since Jun 3 at 7:25 AM, but tracker energy losses are minimal (~0.6 kWh on Jun 9 per the tracker lost energy chart).
-A site-wide outage occurred Jun 3â4, with meter and inverter production at ~0 kWh and availability at 0% both days. Estimated loss ~83 MWh (2 days, ~42 MWh/day expected, full site). Production resumed Jun 5.
-A second multi-day shortfall Jun 21â24 cut meter production sharply (~7â30 MWh/day vs ~40 MWh expected), with no clear root cause in available data.
-30-day EPI averages ~0.98 excluding outage days; availability 93%. Meter-to-inverter ratio 0.98 â normal.
-Tracker Controller 1 comm loss and two transformer vacuum faults remain active alerts for visibility.
-Forecast: rain through Jun 12 with highs to 97Â°F; expect reduced output and possible inverter derating.[DONE]</t>
+          <t>All 40 inverters are online and producing as of Jun 9 at 8:10 PM EDT, with site output tracking irradiance on a light-rain day per the production and expected chart.
+A site-wide outage occurred Jun 3â4, with zero meter and inverter production both days visible on the production meter chart. Cause is undetermined from available data. Estimated loss ~83 MWh (2 days, 100% capacity, ~42 MWh/day expected). Production fully recovered Jun 5.
+A similar full-site outage occurred May 17â19, contributing to the EPI dips on those dates.
+30-day EPI averages 1.00 excluding outage days; inverter availability is 93%, dragged by the Jun 3â4 event. Meter-to-inverter ratio is 0.98 (normal).
+Tracker Controller 1 has been offline since Jun 3 with minimal energy impact (~16â30 kWh/day site-wide); TCU 33 shows a 64Â° tracker error per active alerts. Two transformer vacuum-fault alerts remain unacknowledged.
+Forecast: light rain and highs to 99Â°F through Jun 12; no production risk expected.[DONE]</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="97" customHeight="1">
+          <t>2026-06-10 00:11 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="96" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>S70645</t>
@@ -1343,17 +1341,16 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>INVERTER A20 (125 kW) has been offline since Jun 5 â the meter-to-inverter ratio of 0.97 over 30 days confirms a true outage, not a comm loss.
-A grid overvoltage fault triggered 21 times in 24 hours, followed by a device communication alert on Jun 8 at 3:39 PM EST, classifies this as a forced outage. The remaining 39 inverters are producing normally.
-Estimated loss: ~4.3 MWh (5 days Ã ~860 kWh/day downtime per PV model losses for the sampled A20).
-30-day EPI averages 0.97 and inverter availability 99%; production tracks estimate at 101%. Tracker losses are minor (~17â27 kWh/day).
-Rule tool flags for A20 (0% availability, downtime loss) align with the confirmed outage.
-Weather: clear today (79Â°F), with light-to-heavy rain Jun 11â12 likely reducing output.[DONE]</t>
+          <t>INVERTER A20 has been offline since Jun 5 with zero production while peers operate normally. The meter-to-inverter ratio of 0.97 confirms a true outage, not a comm loss.
+A grid overvoltage fault on Jun 8 at 3:10 PM EDT followed by a device communication alert at 3:39 PM points to a forced outage. The other 39 inverters are online and producing normally under clear skies.
+INVERTER A20 forced outage (Jun 5âpresent, ongoing ~5 days, 125 kW / 2.5% of site capacity). Estimated loss ~5 MWh (5 days Ã ~1 MWh/day expected per PV Model Losses for the sampled inverter).
+30-day EPI averages 0.98; inverter availability 99%. Tracker losses minimal (~23 kWh/day).
+Forecast brings rain and highs near 100Â°F Jun 10â12; possible heat derating and reduced irradiance.[DONE]</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:54 UTC</t>
+          <t>2026-06-10 00:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1427,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1467,7 +1464,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1541,7 +1538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1652,7 +1649,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1736,7 +1733,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1837,7 +1834,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1847,7 +1844,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1884,7 +1881,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1921,7 +1918,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1995,7 +1992,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2022,7 +2019,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2059,12 +2056,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2281,7 +2278,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2328,7 +2325,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -2429,7 +2426,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2439,7 +2436,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2466,7 +2463,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -2503,7 +2500,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2550,7 +2547,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
